--- a/tests/archean/profile.xlsx
+++ b/tests/archean/profile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ttntr\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sophiamail-my.sharepoint.com/personal/01043753_sophiamail_sophia_ac_jp/Documents/PATMO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43711640-811F-4CCA-97B5-0666522CA4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{43711640-811F-4CCA-97B5-0666522CA4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64ABC18D-964C-48D4-80C0-D8E7FDC770D2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D7BD78CA-9E1A-A84E-ABC8-B9A18946ED57}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D7BD78CA-9E1A-A84E-ABC8-B9A18946ED57}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -57,12 +57,6 @@
     <t>Tgas</t>
   </si>
   <si>
-    <t>N2</t>
-  </si>
-  <si>
-    <t>CO2</t>
-  </si>
-  <si>
     <t>O2</t>
   </si>
   <si>
@@ -86,6 +80,14 @@
   <si>
     <t>H2O</t>
   </si>
+  <si>
+    <t>CO2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -95,14 +97,14 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Aptos Narrow"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -472,9 +474,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA7F68D6-EB94-CE47-9BFF-C3E1342F35B3}">
   <dimension ref="A1:P101"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="6" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="11.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -491,40 +499,40 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
-      </c>
-      <c r="N1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" t="s">
-        <v>15</v>
       </c>
       <c r="P1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -540,42 +548,42 @@
       <c r="E2">
         <v>293.0541661580404</v>
       </c>
-      <c r="F2" s="1">
-        <v>6.9273259980806131E+17</v>
-      </c>
-      <c r="G2" s="1">
-        <v>2.184252035959414E+19</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="F2">
+        <v>2.2108556616427028E+19</v>
+      </c>
+      <c r="G2">
+        <v>2.2564587148341056E+17</v>
+      </c>
+      <c r="H2">
         <v>225645871483.41055</v>
       </c>
-      <c r="I2" s="1">
-        <v>2256458714834105.5</v>
-      </c>
-      <c r="J2" s="1">
+      <c r="I2">
+        <v>225645871483410.56</v>
+      </c>
+      <c r="J2">
         <v>99999.999999999985</v>
       </c>
-      <c r="K2" s="1">
-        <v>2.2564587148341056E+16</v>
-      </c>
-      <c r="L2" s="1">
+      <c r="K2">
+        <v>2.2564587148341056E+17</v>
+      </c>
+      <c r="L2">
         <v>34999.999999999993</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2">
         <v>3499.9999999999995</v>
       </c>
-      <c r="N2" s="1">
-        <v>0</v>
+      <c r="N2">
+        <v>44458.103474890449</v>
       </c>
       <c r="O2" s="1">
         <v>4512917429668211</v>
       </c>
       <c r="P2" s="1">
         <f>SUM(F2:O2)</f>
-        <v>2.2564587148341055E+19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2.2564587148341064E+19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -591,32 +599,32 @@
       <c r="E3">
         <v>286.10833231608075</v>
       </c>
-      <c r="F3" s="1">
-        <v>6.1005681190902131E+17</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.9235673820351406E+19</v>
-      </c>
-      <c r="H3" s="1">
+      <c r="F3">
+        <v>1.9469959359592157E+19</v>
+      </c>
+      <c r="G3">
+        <v>1.9871563863999386E+17</v>
+      </c>
+      <c r="H3">
         <v>198715638639.99387</v>
       </c>
-      <c r="I3" s="1">
-        <v>1987156386399938.8</v>
-      </c>
-      <c r="J3" s="1">
+      <c r="I3">
+        <v>198715638639993.88</v>
+      </c>
+      <c r="J3">
         <v>88065.266753441741</v>
       </c>
-      <c r="K3" s="1">
-        <v>1.9871563863999388E+16</v>
-      </c>
-      <c r="L3" s="1">
+      <c r="K3">
+        <v>1.9871563863999386E+17</v>
+      </c>
+      <c r="L3">
         <v>30822.843363704607</v>
       </c>
-      <c r="M3" s="1">
+      <c r="M3">
         <v>3082.284336370461</v>
       </c>
-      <c r="N3" s="1">
-        <v>0</v>
+      <c r="N3">
+        <v>39152.147418683431</v>
       </c>
       <c r="O3" s="1">
         <v>3974312772799877.5</v>
@@ -626,7 +634,7 @@
         <v>1.987156386399939E+19</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -642,42 +650,42 @@
       <c r="E4">
         <v>279.16249847412109</v>
       </c>
-      <c r="F4" s="1">
-        <v>5.3395739802228314E+17</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.6836186633470325E+19</v>
-      </c>
-      <c r="H4" s="1">
+      <c r="F4">
+        <v>1.7041247038477156E+19</v>
+      </c>
+      <c r="G4">
+        <v>1.7392754786642899E+17</v>
+      </c>
+      <c r="H4">
         <v>173927547866.42899</v>
       </c>
-      <c r="I4" s="1">
-        <v>1739275478664290</v>
-      </c>
-      <c r="J4" s="1">
+      <c r="I4">
+        <v>173927547866429</v>
+      </c>
+      <c r="J4">
         <v>77079.87153632284</v>
       </c>
-      <c r="K4" s="1">
-        <v>1.73927547866429E+16</v>
-      </c>
-      <c r="L4" s="1">
+      <c r="K4">
+        <v>1.7392754786642899E+17</v>
+      </c>
+      <c r="L4">
         <v>26977.955037712989</v>
       </c>
-      <c r="M4" s="1">
+      <c r="M4">
         <v>2697.7955037712991</v>
       </c>
-      <c r="N4" s="1">
-        <v>0</v>
+      <c r="N4">
+        <v>34268.249045931043</v>
       </c>
       <c r="O4" s="1">
         <v>3478550957328580</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" si="0"/>
-        <v>1.7392754786642897E+19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.7392754786642899E+19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -693,32 +701,32 @@
       <c r="E5">
         <v>272.21666463216144</v>
       </c>
-      <c r="F5" s="1">
-        <v>4.6427751614491603E+17</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.4639113420830689E+19</v>
-      </c>
-      <c r="H5" s="1">
+      <c r="F5">
+        <v>1.481741404153352E+19</v>
+      </c>
+      <c r="G5">
+        <v>1.5123051054577158E+17</v>
+      </c>
+      <c r="H5">
         <v>151230510545.77158</v>
       </c>
-      <c r="I5" s="1">
-        <v>1512305105457716</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="I5">
+        <v>151230510545771.59</v>
+      </c>
+      <c r="J5">
         <v>67021.173288734426</v>
       </c>
-      <c r="K5" s="1">
-        <v>1.5123051054577158E+16</v>
-      </c>
-      <c r="L5" s="1">
+      <c r="K5">
+        <v>1.5123051054577158E+17</v>
+      </c>
+      <c r="L5">
         <v>23457.410651057049</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5">
         <v>2345.7410651057048</v>
       </c>
-      <c r="N5" s="1">
-        <v>0</v>
+      <c r="N5">
+        <v>29796.342570791196</v>
       </c>
       <c r="O5" s="1">
         <v>3024610210915432</v>
@@ -728,7 +736,7 @@
         <v>1.512305105457716E+19</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -744,32 +752,32 @@
       <c r="E6">
         <v>265.27083079020184</v>
       </c>
-      <c r="F6" s="1">
-        <v>4.0083585487122842E+17</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.2638737260677485E+19</v>
-      </c>
-      <c r="H6" s="1">
+      <c r="F6">
+        <v>1.2792673816375742E+19</v>
+      </c>
+      <c r="G6">
+        <v>1.3056546756898229E+17</v>
+      </c>
+      <c r="H6">
         <v>130565467568.98228</v>
       </c>
-      <c r="I6" s="1">
-        <v>1305654675689823</v>
-      </c>
-      <c r="J6" s="1">
+      <c r="I6">
+        <v>130565467568982.3</v>
+      </c>
+      <c r="J6">
         <v>57862.998649448557</v>
       </c>
-      <c r="K6" s="1">
-        <v>1.3056546756898228E+16</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="K6">
+        <v>1.3056546756898229E+17</v>
+      </c>
+      <c r="L6">
         <v>20252.049527306994</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6">
         <v>2025.2049527306995</v>
       </c>
-      <c r="N6" s="1">
-        <v>0</v>
+      <c r="N6">
+        <v>25724.791813246306</v>
       </c>
       <c r="O6" s="1">
         <v>2611309351379646</v>
@@ -779,7 +787,7 @@
         <v>1.3056546756898228E+19</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -795,42 +803,42 @@
       <c r="E7">
         <v>258.32499694824219</v>
       </c>
-      <c r="F7" s="1">
-        <v>3.4342670911773146E+17</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1.0828572075301329E+19</v>
-      </c>
-      <c r="H7" s="1">
+      <c r="F7">
+        <v>1.0960461286543059E+19</v>
+      </c>
+      <c r="G7">
+        <v>1.118654140010468E+17</v>
+      </c>
+      <c r="H7">
         <v>111865414001.0468</v>
       </c>
-      <c r="I7" s="1">
-        <v>1118654140010468</v>
-      </c>
-      <c r="J7" s="1">
+      <c r="I7">
+        <v>111865414001046.8</v>
+      </c>
+      <c r="J7">
         <v>49575.652887259275</v>
       </c>
-      <c r="K7" s="1">
-        <v>1.118654140010468E+16</v>
-      </c>
-      <c r="L7" s="1">
+      <c r="K7">
+        <v>1.118654140010468E+17</v>
+      </c>
+      <c r="L7">
         <v>17351.478510540746</v>
       </c>
-      <c r="M7" s="1">
+      <c r="M7">
         <v>1735.1478510540746</v>
       </c>
-      <c r="N7" s="1">
-        <v>0</v>
+      <c r="N7">
+        <v>22040.395058970247</v>
       </c>
       <c r="O7" s="1">
         <v>2237308280020936</v>
       </c>
       <c r="P7" s="1">
         <f t="shared" si="0"/>
-        <v>1.1186541400104677E+19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.1186541400104679E+19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -846,42 +854,42 @@
       <c r="E8">
         <v>251.37916310628256</v>
       </c>
-      <c r="F8" s="1">
-        <v>2.9182025886777453E+17</v>
-      </c>
-      <c r="G8" s="1">
-        <v>9.2013714201229988E+18</v>
-      </c>
-      <c r="H8" s="1">
+      <c r="F8">
+        <v>9.3134417476327731E+18</v>
+      </c>
+      <c r="G8">
+        <v>9.5055489877303712E+16</v>
+      </c>
+      <c r="H8">
         <v>95055489877.303711</v>
       </c>
-      <c r="I8" s="1">
-        <v>950554898773037.13</v>
-      </c>
-      <c r="J8" s="1">
+      <c r="I8">
+        <v>95055489877303.719</v>
+      </c>
+      <c r="J8">
         <v>42125.960139400187</v>
       </c>
-      <c r="K8" s="1">
-        <v>9505548987730370</v>
-      </c>
-      <c r="L8" s="1">
+      <c r="K8">
+        <v>9.5055489877303712E+16</v>
+      </c>
+      <c r="L8">
         <v>14744.086048790065</v>
       </c>
-      <c r="M8" s="1">
+      <c r="M8">
         <v>1474.4086048790064</v>
       </c>
-      <c r="N8" s="1">
-        <v>0</v>
+      <c r="N8">
+        <v>18728.402948565643</v>
       </c>
       <c r="O8" s="1">
         <v>1901109797546074.3</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="0"/>
-        <v>9.5055489877303726E+18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>9.5055489877303706E+18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -897,42 +905,42 @@
       <c r="E9">
         <v>244.43332926432291</v>
       </c>
-      <c r="F9" s="1">
-        <v>2.4576331508221226E+17</v>
-      </c>
-      <c r="G9" s="1">
-        <v>7.7491520029690132E+18</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="F9">
+        <v>7.8435346730345318E+18</v>
+      </c>
+      <c r="G9">
+        <v>8.0053223171167504E+16</v>
+      </c>
+      <c r="H9">
         <v>80053223171.167496</v>
       </c>
-      <c r="I9" s="1">
-        <v>800532231711675</v>
-      </c>
-      <c r="J9" s="1">
+      <c r="I9">
+        <v>80053223171167.5</v>
+      </c>
+      <c r="J9">
         <v>35477.371088109183</v>
       </c>
-      <c r="K9" s="1">
-        <v>8005322317116750</v>
-      </c>
-      <c r="L9" s="1">
+      <c r="K9">
+        <v>8.0053223171167504E+16</v>
+      </c>
+      <c r="L9">
         <v>12417.079880838211</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9">
         <v>1241.7079880838212</v>
       </c>
-      <c r="N9" s="1">
-        <v>0</v>
+      <c r="N9">
+        <v>15772.566348522449</v>
       </c>
       <c r="O9" s="1">
         <v>1601064463423350</v>
       </c>
       <c r="P9" s="1">
         <f t="shared" si="0"/>
-        <v>8.0053223171167498E+18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8.0053223171167488E+18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -948,32 +956,32 @@
       <c r="E10">
         <v>237.48749542236328</v>
       </c>
-      <c r="F10" s="1">
-        <v>2.0498042713934998E+17</v>
-      </c>
-      <c r="G10" s="1">
-        <v>6.4632286027106263E+18</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="F10">
+        <v>6.5419490578693243E+18</v>
+      </c>
+      <c r="G10">
+        <v>6.6768890523870104E+16</v>
+      </c>
+      <c r="H10">
         <v>66768890523.87011</v>
       </c>
-      <c r="I10" s="1">
-        <v>667688905238701.13</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="I10">
+        <v>66768890523870.109</v>
+      </c>
+      <c r="J10">
         <v>29590.12282605797</v>
       </c>
-      <c r="K10" s="1">
-        <v>6676889052387011</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="K10">
+        <v>6.6768890523870104E+16</v>
+      </c>
+      <c r="L10">
         <v>10356.542989120289</v>
       </c>
-      <c r="M10" s="1">
+      <c r="M10">
         <v>1035.6542989120289</v>
       </c>
-      <c r="N10" s="1">
-        <v>0</v>
+      <c r="N10">
+        <v>13155.207424356033</v>
       </c>
       <c r="O10" s="1">
         <v>1335377810477402.3</v>
@@ -983,7 +991,7 @@
         <v>6.6768890523870106E+18</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -999,32 +1007,32 @@
       <c r="E11">
         <v>230.54166158040366</v>
       </c>
-      <c r="F11" s="1">
-        <v>1.6917537582879021E+17</v>
-      </c>
-      <c r="G11" s="1">
-        <v>5.3342611447854367E+18</v>
-      </c>
-      <c r="H11" s="1">
+      <c r="F11">
+        <v>5.3992310678787891E+18</v>
+      </c>
+      <c r="G11">
+        <v>5.5106003561833024E+16</v>
+      </c>
+      <c r="H11">
         <v>55106003561.833023</v>
       </c>
-      <c r="I11" s="1">
-        <v>551060035618330.25</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="I11">
+        <v>55106003561833.023</v>
+      </c>
+      <c r="J11">
         <v>24421.454378740716</v>
       </c>
-      <c r="K11" s="1">
-        <v>5510600356183302</v>
-      </c>
-      <c r="L11" s="1">
+      <c r="K11">
+        <v>5.5106003561833024E+16</v>
+      </c>
+      <c r="L11">
         <v>8547.50903255925</v>
       </c>
-      <c r="M11" s="1">
+      <c r="M11">
         <v>854.7509032559251</v>
       </c>
-      <c r="N11" s="1">
-        <v>0</v>
+      <c r="N11">
+        <v>10857.315457773713</v>
       </c>
       <c r="O11" s="1">
         <v>1102120071236660.5</v>
@@ -1034,7 +1042,7 @@
         <v>5.5106003561833032E+18</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1050,32 +1058,32 @@
       <c r="E12">
         <v>223.595827738444</v>
       </c>
-      <c r="F12" s="1">
-        <v>1.3803325857927754E+17</v>
-      </c>
-      <c r="G12" s="1">
-        <v>4.3523204504225306E+18</v>
-      </c>
-      <c r="H12" s="1">
+      <c r="F12">
+        <v>4.4053305894589373E+18</v>
+      </c>
+      <c r="G12">
+        <v>4.4961988124199696E+16</v>
+      </c>
+      <c r="H12">
         <v>44961988124.199699</v>
       </c>
-      <c r="I12" s="1">
-        <v>449619881241997</v>
-      </c>
-      <c r="J12" s="1">
+      <c r="I12">
+        <v>44961988124199.695</v>
+      </c>
+      <c r="J12">
         <v>19925.907719302228</v>
       </c>
-      <c r="K12" s="1">
-        <v>4496198812419969.5</v>
-      </c>
-      <c r="L12" s="1">
+      <c r="K12">
+        <v>4.4961988124199696E+16</v>
+      </c>
+      <c r="L12">
         <v>6974.06770175578</v>
       </c>
-      <c r="M12" s="1">
+      <c r="M12">
         <v>697.406770175578</v>
       </c>
-      <c r="N12" s="1">
-        <v>0</v>
+      <c r="N12">
+        <v>8858.6806721585708</v>
       </c>
       <c r="O12" s="1">
         <v>899239762483994</v>
@@ -1085,7 +1093,7 @@
         <v>4.49619881241997E+18</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1101,32 +1109,32 @@
       <c r="E13">
         <v>216.64999389648438</v>
       </c>
-      <c r="F13" s="1">
-        <v>1.1777019611975434E+17</v>
-      </c>
-      <c r="G13" s="1">
-        <v>3.7134067419547965E+18</v>
-      </c>
-      <c r="H13" s="1">
+      <c r="F13">
+        <v>3.7586350770307773E+18</v>
+      </c>
+      <c r="G13">
+        <v>3.836163989622724E+16</v>
+      </c>
+      <c r="H13">
         <v>38361639896.227234</v>
       </c>
-      <c r="I13" s="1">
-        <v>383616398962272.38</v>
-      </c>
-      <c r="J13" s="1">
+      <c r="I13">
+        <v>38361639896227.242</v>
+      </c>
+      <c r="J13">
         <v>17000.816209946734</v>
       </c>
-      <c r="K13" s="1">
-        <v>3836163989622723.5</v>
-      </c>
-      <c r="L13" s="1">
+      <c r="K13">
+        <v>3.836163989622724E+16</v>
+      </c>
+      <c r="L13">
         <v>5950.2856734813558</v>
       </c>
-      <c r="M13" s="1">
+      <c r="M13">
         <v>595.02856734813565</v>
       </c>
-      <c r="N13" s="1">
-        <v>0</v>
+      <c r="N13">
+        <v>7558.2404621940677</v>
       </c>
       <c r="O13" s="1">
         <v>767232797924544.75</v>
@@ -1136,7 +1144,7 @@
         <v>3.8361639896227236E+18</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1152,42 +1160,42 @@
       <c r="E14">
         <v>216.64999389648438</v>
       </c>
-      <c r="F14" s="1">
-        <v>1.0058093849908266E+17</v>
-      </c>
-      <c r="G14" s="1">
-        <v>3.1714130352202506E+18</v>
-      </c>
-      <c r="H14" s="1">
+      <c r="F14">
+        <v>3.2100400269259228E+18</v>
+      </c>
+      <c r="G14">
+        <v>3.2762531355581104E+16</v>
+      </c>
+      <c r="H14">
         <v>32762531355.581104</v>
       </c>
-      <c r="I14" s="1">
-        <v>327625313555811.06</v>
-      </c>
-      <c r="J14" s="1">
+      <c r="I14">
+        <v>32762531355581.105</v>
+      </c>
+      <c r="J14">
         <v>14519.446396336923</v>
       </c>
-      <c r="K14" s="1">
-        <v>3276253135558110.5</v>
-      </c>
-      <c r="L14" s="1">
+      <c r="K14">
+        <v>3.2762531355581104E+16</v>
+      </c>
+      <c r="L14">
         <v>5081.8062387179225</v>
       </c>
-      <c r="M14" s="1">
+      <c r="M14">
         <v>508.18062387179231</v>
       </c>
-      <c r="N14" s="1">
-        <v>0</v>
+      <c r="N14">
+        <v>6455.0705028647226</v>
       </c>
       <c r="O14" s="1">
         <v>655250627111622.13</v>
       </c>
       <c r="P14" s="1">
         <f t="shared" si="0"/>
-        <v>3.2762531355581102E+18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+        <v>3.2762531355581097E+18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1203,32 +1211,32 @@
       <c r="E15">
         <v>216.64999389648438</v>
       </c>
-      <c r="F15" s="1">
-        <v>8.5900554831965168E+16</v>
-      </c>
-      <c r="G15" s="1">
-        <v>2.708526519955179E+18</v>
-      </c>
-      <c r="H15" s="1">
+      <c r="F15">
+        <v>2.7415156734520637E+18</v>
+      </c>
+      <c r="G15">
+        <v>2.7980645867305568E+16</v>
+      </c>
+      <c r="H15">
         <v>27980645867.305569</v>
       </c>
-      <c r="I15" s="1">
-        <v>279806458673055.72</v>
-      </c>
-      <c r="J15" s="1">
+      <c r="I15">
+        <v>27980645867305.57</v>
+      </c>
+      <c r="J15">
         <v>12400.247202999546</v>
       </c>
-      <c r="K15" s="1">
-        <v>2798064586730557</v>
-      </c>
-      <c r="L15" s="1">
+      <c r="K15">
+        <v>2.7980645867305568E+16</v>
+      </c>
+      <c r="L15">
         <v>4340.0865210498405</v>
       </c>
-      <c r="M15" s="1">
+      <c r="M15">
         <v>434.00865210498409</v>
       </c>
-      <c r="N15" s="1">
-        <v>0</v>
+      <c r="N15">
+        <v>5512.9147326517477</v>
       </c>
       <c r="O15" s="1">
         <v>559612917346111.44</v>
@@ -1238,7 +1246,7 @@
         <v>2.7980645867305569E+18</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1254,32 +1262,32 @@
       <c r="E16">
         <v>216.64999389648438</v>
       </c>
-      <c r="F16" s="1">
-        <v>7.3362860106010576E+16</v>
-      </c>
-      <c r="G16" s="1">
-        <v>2.3132010330502497E+18</v>
-      </c>
-      <c r="H16" s="1">
+      <c r="F16">
+        <v>2.3413752242151603E+18</v>
+      </c>
+      <c r="G16">
+        <v>2.3896704886882744E+16</v>
+      </c>
+      <c r="H16">
         <v>23896704886.882744</v>
       </c>
-      <c r="I16" s="1">
-        <v>238967048868827.47</v>
-      </c>
-      <c r="J16" s="1">
+      <c r="I16">
+        <v>23896704886882.746</v>
+      </c>
+      <c r="J16">
         <v>10590.357682941087</v>
       </c>
-      <c r="K16" s="1">
-        <v>2389670488688274.5</v>
-      </c>
-      <c r="L16" s="1">
+      <c r="K16">
+        <v>2.3896704886882744E+16</v>
+      </c>
+      <c r="L16">
         <v>3706.6251890293806</v>
       </c>
-      <c r="M16" s="1">
+      <c r="M16">
         <v>370.66251890293807</v>
       </c>
-      <c r="N16" s="1">
-        <v>0</v>
+      <c r="N16">
+        <v>4708.2721770429598</v>
       </c>
       <c r="O16" s="1">
         <v>477934097737654.94</v>
@@ -1289,7 +1297,7 @@
         <v>2.3896704886882749E+18</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1305,42 +1313,42 @@
       <c r="E17">
         <v>216.64999389648438</v>
       </c>
-      <c r="F17" s="1">
-        <v>6.26551161801262E+16</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1.9755756422843853E+18</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="F17">
+        <v>1.9996376433864105E+18</v>
+      </c>
+      <c r="G17">
+        <v>2.0408839279797368E+16</v>
+      </c>
+      <c r="H17">
         <v>20408839279.797367</v>
       </c>
-      <c r="I17" s="1">
-        <v>204088392797973.69</v>
-      </c>
-      <c r="J17" s="1">
+      <c r="I17">
+        <v>20408839279797.371</v>
+      </c>
+      <c r="J17">
         <v>9044.6322574520582</v>
       </c>
-      <c r="K17" s="1">
-        <v>2040883927979736.8</v>
-      </c>
-      <c r="L17" s="1">
+      <c r="K17">
+        <v>2.0408839279797368E+16</v>
+      </c>
+      <c r="L17">
         <v>3165.6212901082204</v>
       </c>
-      <c r="M17" s="1">
+      <c r="M17">
         <v>316.56212901082205</v>
       </c>
-      <c r="N17" s="1">
-        <v>0</v>
+      <c r="N17">
+        <v>4021.0719679413569</v>
       </c>
       <c r="O17" s="1">
         <v>408176785595947.38</v>
       </c>
       <c r="P17" s="1">
         <f t="shared" si="0"/>
-        <v>2.0408839279797366E+18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2.0408839279797363E+18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1356,32 +1364,32 @@
       <c r="E18">
         <v>216.64999389648438</v>
       </c>
-      <c r="F18" s="1">
-        <v>5.3510230897111432E+16</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1.6872286768957955E+18</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="F18">
+        <v>1.7077786864291643E+18</v>
+      </c>
+      <c r="G18">
+        <v>1.743004831503921E+16</v>
+      </c>
+      <c r="H18">
         <v>17430048315.039207</v>
       </c>
-      <c r="I18" s="1">
-        <v>174300483150392.09</v>
-      </c>
-      <c r="J18" s="1">
+      <c r="I18">
+        <v>17430048315039.211</v>
+      </c>
+      <c r="J18">
         <v>7724.514612411449</v>
       </c>
-      <c r="K18" s="1">
-        <v>1743004831503921</v>
-      </c>
-      <c r="L18" s="1">
+      <c r="K18">
+        <v>1.743004831503921E+16</v>
+      </c>
+      <c r="L18">
         <v>2703.5801143440071</v>
       </c>
-      <c r="M18" s="1">
+      <c r="M18">
         <v>270.35801143440074</v>
       </c>
-      <c r="N18" s="1">
-        <v>0</v>
+      <c r="N18">
+        <v>3434.1726993189154</v>
       </c>
       <c r="O18" s="1">
         <v>348600966300784.19</v>
@@ -1391,7 +1399,7 @@
         <v>1.7430048315039209E+18</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1407,32 +1415,32 @@
       <c r="E19">
         <v>216.64999389648438</v>
       </c>
-      <c r="F19" s="1">
-        <v>4.5700095781969272E+16</v>
-      </c>
-      <c r="G19" s="1">
-        <v>1.4409676588479357E+18</v>
-      </c>
-      <c r="H19" s="1">
+      <c r="F19">
+        <v>1.458518272781953E+18</v>
+      </c>
+      <c r="G19">
+        <v>1.4886029533553056E+16</v>
+      </c>
+      <c r="H19">
         <v>14886029533.553055</v>
       </c>
-      <c r="I19" s="1">
-        <v>148860295335530.56</v>
-      </c>
-      <c r="J19" s="1">
+      <c r="I19">
+        <v>14886029533553.057</v>
+      </c>
+      <c r="J19">
         <v>6597.0759560949782</v>
       </c>
-      <c r="K19" s="1">
-        <v>1488602953355305.5</v>
-      </c>
-      <c r="L19" s="1">
+      <c r="K19">
+        <v>1.4886029533553056E+16</v>
+      </c>
+      <c r="L19">
         <v>2308.9765846332425</v>
       </c>
-      <c r="M19" s="1">
+      <c r="M19">
         <v>230.89765846332423</v>
       </c>
-      <c r="N19" s="1">
-        <v>0</v>
+      <c r="N19">
+        <v>2932.9348548778244</v>
       </c>
       <c r="O19" s="1">
         <v>297720590671061.13</v>
@@ -1442,7 +1450,7 @@
         <v>1.4886029533553055E+18</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1458,42 +1466,42 @@
       <c r="E20">
         <v>216.64999389648438</v>
       </c>
-      <c r="F20" s="1">
-        <v>3.9029896142606752E+16</v>
-      </c>
-      <c r="G20" s="1">
-        <v>1.2306498948713285E+18</v>
-      </c>
-      <c r="H20" s="1">
+      <c r="F20">
+        <v>1.245638892757717E+18</v>
+      </c>
+      <c r="G20">
+        <v>1.2713325360240998E+16</v>
+      </c>
+      <c r="H20">
         <v>12713325360.240999</v>
       </c>
-      <c r="I20" s="1">
-        <v>127133253602409.98</v>
-      </c>
-      <c r="J20" s="1">
+      <c r="I20">
+        <v>12713325360241</v>
+      </c>
+      <c r="J20">
         <v>5634.1936489521277</v>
       </c>
-      <c r="K20" s="1">
-        <v>1271332536024099.8</v>
-      </c>
-      <c r="L20" s="1">
+      <c r="K20">
+        <v>1.2713325360240998E+16</v>
+      </c>
+      <c r="L20">
         <v>1971.9677771332445</v>
       </c>
-      <c r="M20" s="1">
+      <c r="M20">
         <v>197.19677771332445</v>
       </c>
-      <c r="N20" s="1">
-        <v>0</v>
+      <c r="N20">
+        <v>2504.8556424268431</v>
       </c>
       <c r="O20" s="1">
         <v>254266507204819.97</v>
       </c>
       <c r="P20" s="1">
         <f t="shared" si="0"/>
-        <v>1.2713325360240998E+18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.2713325360240996E+18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1509,42 +1517,42 @@
       <c r="E21">
         <v>216.64999389648438</v>
       </c>
-      <c r="F21" s="1">
-        <v>3.3333251645036848E+16</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1.0510292541594337E+18</v>
-      </c>
-      <c r="H21" s="1">
+      <c r="F21">
+        <v>1.0638305190315812E+18</v>
+      </c>
+      <c r="G21">
+        <v>1.0857740228919772E+16</v>
+      </c>
+      <c r="H21">
         <v>10857740228.919771</v>
       </c>
-      <c r="I21" s="1">
-        <v>108577402289197.72</v>
-      </c>
-      <c r="J21" s="1">
+      <c r="I21">
+        <v>10857740228919.771</v>
+      </c>
+      <c r="J21">
         <v>4811.8497172318212</v>
       </c>
-      <c r="K21" s="1">
-        <v>1085774022891977.1</v>
-      </c>
-      <c r="L21" s="1">
+      <c r="K21">
+        <v>1.0857740228919772E+16</v>
+      </c>
+      <c r="L21">
         <v>1684.1474010311374</v>
       </c>
-      <c r="M21" s="1">
+      <c r="M21">
         <v>168.41474010311376</v>
       </c>
-      <c r="N21" s="1">
-        <v>0</v>
+      <c r="N21">
+        <v>2139.2571263431469</v>
       </c>
       <c r="O21" s="1">
         <v>217154804578395.44</v>
       </c>
       <c r="P21" s="1">
         <f t="shared" si="0"/>
-        <v>1.0857740228919771E+18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.0857740228919772E+18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1560,42 +1568,42 @@
       <c r="E22">
         <v>217.58097839355469</v>
       </c>
-      <c r="F22" s="1">
-        <v>2.887452077138386E+16</v>
-      </c>
-      <c r="G22" s="1">
-        <v>9.104412120885097E+17</v>
-      </c>
-      <c r="H22" s="1">
+      <c r="F22">
+        <v>9.215301509171296E+17</v>
+      </c>
+      <c r="G22">
+        <v>9405384422401960</v>
+      </c>
+      <c r="H22">
         <v>9405384422.4019604</v>
       </c>
-      <c r="I22" s="1">
-        <v>94053844224019.594</v>
-      </c>
-      <c r="J22" s="1">
+      <c r="I22">
+        <v>9405384422401.9609</v>
+      </c>
+      <c r="J22">
         <v>4168.2058530786999</v>
       </c>
-      <c r="K22" s="1">
-        <v>940538442240196</v>
-      </c>
-      <c r="L22" s="1">
+      <c r="K22">
+        <v>9405384422401960</v>
+      </c>
+      <c r="L22">
         <v>1458.8720485775448</v>
       </c>
-      <c r="M22" s="1">
+      <c r="M22">
         <v>145.88720485775448</v>
       </c>
-      <c r="N22" s="1">
-        <v>0</v>
+      <c r="N22">
+        <v>1853.1052712081687</v>
       </c>
       <c r="O22" s="1">
         <v>188107688448039.19</v>
       </c>
       <c r="P22" s="1">
         <f t="shared" si="0"/>
-        <v>9.4053844224019597E+17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+        <v>9.4053844224019584E+17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1611,42 +1619,42 @@
       <c r="E23">
         <v>218.57426452636719</v>
       </c>
-      <c r="F23" s="1">
-        <v>2.5067400726109924E+16</v>
-      </c>
-      <c r="G23" s="1">
-        <v>7.9039908165700467E+17</v>
-      </c>
-      <c r="H23" s="1">
+      <c r="F23">
+        <v>8.0002593833958605E+17</v>
+      </c>
+      <c r="G23">
+        <v>8165279769183932</v>
+      </c>
+      <c r="H23">
         <v>8165279769.1839323</v>
       </c>
-      <c r="I23" s="1">
-        <v>81652797691839.328</v>
-      </c>
-      <c r="J23" s="1">
+      <c r="I23">
+        <v>8165279769183.9326</v>
+      </c>
+      <c r="J23">
         <v>3618.6258208514314</v>
       </c>
-      <c r="K23" s="1">
-        <v>816527976918393.25</v>
-      </c>
-      <c r="L23" s="1">
+      <c r="K23">
+        <v>8165279769183932</v>
+      </c>
+      <c r="L23">
         <v>1266.519037298001</v>
       </c>
-      <c r="M23" s="1">
+      <c r="M23">
         <v>126.6519037298001</v>
       </c>
-      <c r="N23" s="1">
-        <v>0</v>
+      <c r="N23">
+        <v>1608.7724118032336</v>
       </c>
       <c r="O23" s="1">
         <v>163305595383678.66</v>
       </c>
       <c r="P23" s="1">
         <f t="shared" si="0"/>
-        <v>8.1652797691839322E+17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8.1652797691839309E+17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1662,32 +1670,32 @@
       <c r="E24">
         <v>219.56723022460938</v>
       </c>
-      <c r="F24" s="1">
-        <v>2.1789994912326632E+16</v>
-      </c>
-      <c r="G24" s="1">
-        <v>6.8705934676644403E+17</v>
-      </c>
-      <c r="H24" s="1">
+      <c r="F24">
+        <v>6.9542755216704051E+17</v>
+      </c>
+      <c r="G24">
+        <v>7097720524446737</v>
+      </c>
+      <c r="H24">
         <v>7097720524.4467363</v>
       </c>
-      <c r="I24" s="1">
-        <v>70977205244467.375</v>
-      </c>
-      <c r="J24" s="1">
+      <c r="I24">
+        <v>7097720524446.7373</v>
+      </c>
+      <c r="J24">
         <v>3145.513134269137</v>
       </c>
-      <c r="K24" s="1">
-        <v>709772052444673.63</v>
-      </c>
-      <c r="L24" s="1">
+      <c r="K24">
+        <v>7097720524446737</v>
+      </c>
+      <c r="L24">
         <v>1100.9295969941979</v>
       </c>
-      <c r="M24" s="1">
+      <c r="M24">
         <v>110.09295969941979</v>
       </c>
-      <c r="N24" s="1">
-        <v>0</v>
+      <c r="N24">
+        <v>1398.4354840496428</v>
       </c>
       <c r="O24" s="1">
         <v>141954410488934.75</v>
@@ -1697,7 +1705,7 @@
         <v>7.0977205244467379E+17</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1713,32 +1721,32 @@
       <c r="E25">
         <v>220.55989074707031</v>
       </c>
-      <c r="F25" s="1">
-        <v>1.8964903360035328E+16</v>
-      </c>
-      <c r="G25" s="1">
-        <v>5.9798151245384256E+17</v>
-      </c>
-      <c r="H25" s="1">
+      <c r="F25">
+        <v>6.052647728381513E+17</v>
+      </c>
+      <c r="G25">
+        <v>6177494963366143</v>
+      </c>
+      <c r="H25">
         <v>6177494963.3661432</v>
       </c>
-      <c r="I25" s="1">
-        <v>61774949633661.43</v>
-      </c>
-      <c r="J25" s="1">
+      <c r="I25">
+        <v>6177494963366.1436</v>
+      </c>
+      <c r="J25">
         <v>2737.6946552378249</v>
       </c>
-      <c r="K25" s="1">
-        <v>617749496336614.25</v>
-      </c>
-      <c r="L25" s="1">
+      <c r="K25">
+        <v>6177494963366143</v>
+      </c>
+      <c r="L25">
         <v>958.19312933323874</v>
       </c>
-      <c r="M25" s="1">
+      <c r="M25">
         <v>95.819312933323872</v>
       </c>
-      <c r="N25" s="1">
-        <v>0</v>
+      <c r="N25">
+        <v>1217.1271226521778</v>
       </c>
       <c r="O25" s="1">
         <v>123549899267322.86</v>
@@ -1748,7 +1756,7 @@
         <v>6.1774949633661414E+17</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1764,42 +1772,42 @@
       <c r="E26">
         <v>221.55224609375</v>
       </c>
-      <c r="F26" s="1">
-        <v>1.6526551268440496E+16</v>
-      </c>
-      <c r="G26" s="1">
-        <v>5.2109794263299686E+17</v>
-      </c>
-      <c r="H26" s="1">
+      <c r="F26">
+        <v>5.2744478099318214E+17</v>
+      </c>
+      <c r="G26">
+        <v>5383243209018563</v>
+      </c>
+      <c r="H26">
         <v>5383243209.0185623</v>
       </c>
-      <c r="I26" s="1">
-        <v>53832432090185.625</v>
-      </c>
-      <c r="J26" s="1">
+      <c r="I26">
+        <v>5383243209018.5635</v>
+      </c>
+      <c r="J26">
         <v>2385.7042779594294</v>
       </c>
-      <c r="K26" s="1">
-        <v>538324320901856.25</v>
-      </c>
-      <c r="L26" s="1">
+      <c r="K26">
+        <v>5383243209018563</v>
+      </c>
+      <c r="L26">
         <v>834.99649728580027</v>
       </c>
-      <c r="M26" s="1">
+      <c r="M26">
         <v>83.499649728580039</v>
       </c>
-      <c r="N26" s="1">
-        <v>0</v>
+      <c r="N26">
+        <v>1060.6388765000913</v>
       </c>
       <c r="O26" s="1">
         <v>107664864180371.25</v>
       </c>
       <c r="P26" s="1">
         <f t="shared" si="0"/>
-        <v>5.3832432090185626E+17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+        <v>5.3832432090185619E+17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1815,32 +1823,32 @@
       <c r="E27">
         <v>222.54428100585938</v>
       </c>
-      <c r="F27" s="1">
-        <v>1.4419306366952836E+16</v>
-      </c>
-      <c r="G27" s="1">
-        <v>4.5465449868918899E+17</v>
-      </c>
-      <c r="H27" s="1">
+      <c r="F27">
+        <v>4.6019207306211968E+17</v>
+      </c>
+      <c r="G27">
+        <v>4696843994723027</v>
+      </c>
+      <c r="H27">
         <v>4696843994.7230272</v>
       </c>
-      <c r="I27" s="1">
-        <v>46968439947230.273</v>
-      </c>
-      <c r="J27" s="1">
+      <c r="I27">
+        <v>4696843994723.0273</v>
+      </c>
+      <c r="J27">
         <v>2081.5111589880507</v>
       </c>
-      <c r="K27" s="1">
-        <v>469684399472302.75</v>
-      </c>
-      <c r="L27" s="1">
+      <c r="K27">
+        <v>4696843994723027</v>
+      </c>
+      <c r="L27">
         <v>728.52890564581776</v>
       </c>
-      <c r="M27" s="1">
+      <c r="M27">
         <v>72.852890564581784</v>
       </c>
-      <c r="N27" s="1">
-        <v>0</v>
+      <c r="N27">
+        <v>925.40038490429924</v>
       </c>
       <c r="O27" s="1">
         <v>93936879894460.547</v>
@@ -1850,7 +1858,7 @@
         <v>4.6968439947230266E+17</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1866,42 +1874,42 @@
       <c r="E28">
         <v>223.5360107421875</v>
       </c>
-      <c r="F28" s="1">
-        <v>1.259591846529687E+16</v>
-      </c>
-      <c r="G28" s="1">
-        <v>3.9716133700401178E+17</v>
-      </c>
-      <c r="H28" s="1">
+      <c r="F28">
+        <v>4.0199865951605792E+17</v>
+      </c>
+      <c r="G28">
+        <v>4102906374008386</v>
+      </c>
+      <c r="H28">
         <v>4102906374.0083861</v>
       </c>
-      <c r="I28" s="1">
-        <v>41029063740083.859</v>
-      </c>
-      <c r="J28" s="1">
+      <c r="I28">
+        <v>4102906374008.3862</v>
+      </c>
+      <c r="J28">
         <v>1818.294457166716</v>
       </c>
-      <c r="K28" s="1">
-        <v>410290637400838.63</v>
-      </c>
-      <c r="L28" s="1">
+      <c r="K28">
+        <v>4102906374008386</v>
+      </c>
+      <c r="L28">
         <v>636.40306000835062</v>
       </c>
-      <c r="M28" s="1">
+      <c r="M28">
         <v>63.640306000835061</v>
       </c>
-      <c r="N28" s="1">
-        <v>0</v>
+      <c r="N28">
+        <v>808.37923124537633</v>
       </c>
       <c r="O28" s="1">
         <v>82058127480167.719</v>
       </c>
       <c r="P28" s="1">
         <f t="shared" si="0"/>
-        <v>4.1029063740083866E+17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+        <v>4.1029063740083859E+17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1917,42 +1925,42 @@
       <c r="E29">
         <v>224.52743530273438</v>
       </c>
-      <c r="F29" s="1">
-        <v>1.1016191457459968E+16</v>
-      </c>
-      <c r="G29" s="1">
-        <v>3.4735103597178259E+17</v>
-      </c>
-      <c r="H29" s="1">
+      <c r="F29">
+        <v>3.515816818814873E+17</v>
+      </c>
+      <c r="G29">
+        <v>3588337148468829</v>
+      </c>
+      <c r="H29">
         <v>3588337148.4688287</v>
       </c>
-      <c r="I29" s="1">
-        <v>35883371484688.289</v>
-      </c>
-      <c r="J29" s="1">
+      <c r="I29">
+        <v>3588337148468.8291</v>
+      </c>
+      <c r="J29">
         <v>1590.2516296349088</v>
       </c>
-      <c r="K29" s="1">
-        <v>358833714846882.88</v>
-      </c>
-      <c r="L29" s="1">
+      <c r="K29">
+        <v>3588337148468829</v>
+      </c>
+      <c r="L29">
         <v>556.58807037221811</v>
       </c>
-      <c r="M29" s="1">
+      <c r="M29">
         <v>55.658807037221813</v>
       </c>
-      <c r="N29" s="1">
-        <v>0</v>
+      <c r="N29">
+        <v>706.99571501421951</v>
       </c>
       <c r="O29" s="1">
         <v>71766742969376.578</v>
       </c>
       <c r="P29" s="1">
         <f t="shared" si="0"/>
-        <v>3.5883371484688294E+17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+        <v>3.5883371484688288E+17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1968,42 +1976,42 @@
       <c r="E30">
         <v>225.5185546875</v>
       </c>
-      <c r="F30" s="1">
-        <v>9645888312488330</v>
-      </c>
-      <c r="G30" s="1">
-        <v>3.0414406931372154E+17</v>
-      </c>
-      <c r="H30" s="1">
+      <c r="F30">
+        <v>3.0784846552835546E+17</v>
+      </c>
+      <c r="G30">
+        <v>3141984187125222.5</v>
+      </c>
+      <c r="H30">
         <v>3141984187.1252227</v>
       </c>
-      <c r="I30" s="1">
-        <v>31419841871252.227</v>
-      </c>
-      <c r="J30" s="1">
+      <c r="I30">
+        <v>3141984187125.2227</v>
+      </c>
+      <c r="J30">
         <v>1392.4403608493321</v>
       </c>
-      <c r="K30" s="1">
-        <v>314198418712522.25</v>
-      </c>
-      <c r="L30" s="1">
+      <c r="K30">
+        <v>3141984187125222.5</v>
+      </c>
+      <c r="L30">
         <v>487.35412629726619</v>
       </c>
-      <c r="M30" s="1">
+      <c r="M30">
         <v>48.735412629726625</v>
       </c>
-      <c r="N30" s="1">
-        <v>0</v>
+      <c r="N30">
+        <v>619.05257645253414</v>
       </c>
       <c r="O30" s="1">
         <v>62839683742504.453</v>
       </c>
       <c r="P30" s="1">
         <f t="shared" si="0"/>
-        <v>3.141984187125223E+17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+        <v>3.1419841871252243E+17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2019,42 +2027,42 @@
       <c r="E31">
         <v>226.50933837890625</v>
       </c>
-      <c r="F31" s="1">
-        <v>8455804257842741</v>
-      </c>
-      <c r="G31" s="1">
-        <v>2.6661958266414416E+17</v>
-      </c>
-      <c r="H31" s="1">
+      <c r="F31">
+        <v>2.698669403226279E+17</v>
+      </c>
+      <c r="G31">
+        <v>2754334531654382</v>
+      </c>
+      <c r="H31">
         <v>2754334531.6543818</v>
       </c>
-      <c r="I31" s="1">
-        <v>27543345316543.82</v>
-      </c>
-      <c r="J31" s="1">
+      <c r="I31">
+        <v>2754334531654.3818</v>
+      </c>
+      <c r="J31">
         <v>1220.6447711838059</v>
       </c>
-      <c r="K31" s="1">
-        <v>275433453165438.19</v>
-      </c>
-      <c r="L31" s="1">
+      <c r="K31">
+        <v>2754334531654382</v>
+      </c>
+      <c r="L31">
         <v>427.22566991433206</v>
       </c>
-      <c r="M31" s="1">
+      <c r="M31">
         <v>42.722566991433204</v>
       </c>
-      <c r="N31" s="1">
-        <v>0</v>
+      <c r="N31">
+        <v>542.67551543373622</v>
       </c>
       <c r="O31" s="1">
         <v>55086690633087.641</v>
       </c>
       <c r="P31" s="1">
         <f t="shared" si="0"/>
-        <v>2.7543345316543818E+17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2.7543345316543811E+17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2070,32 +2078,32 @@
       <c r="E32">
         <v>227.49983215332031</v>
       </c>
-      <c r="F32" s="1">
-        <v>7421012225070120</v>
-      </c>
-      <c r="G32" s="1">
-        <v>2.3399160175196483E+17</v>
-      </c>
-      <c r="H32" s="1">
+      <c r="F32">
+        <v>2.3684155902958646E+17</v>
+      </c>
+      <c r="G32">
+        <v>2417268613140132.5</v>
+      </c>
+      <c r="H32">
         <v>2417268613.1401324</v>
       </c>
-      <c r="I32" s="1">
-        <v>24172686131401.324</v>
-      </c>
-      <c r="J32" s="1">
+      <c r="I32">
+        <v>2417268613140.1328</v>
+      </c>
+      <c r="J32">
         <v>1071.2664926013722</v>
       </c>
-      <c r="K32" s="1">
-        <v>241726861314013.25</v>
-      </c>
-      <c r="L32" s="1">
+      <c r="K32">
+        <v>2417268613140132.5</v>
+      </c>
+      <c r="L32">
         <v>374.94327241048029</v>
       </c>
-      <c r="M32" s="1">
+      <c r="M32">
         <v>37.494327241048026</v>
       </c>
-      <c r="N32" s="1">
-        <v>0</v>
+      <c r="N32">
+        <v>476.26476577254778</v>
       </c>
       <c r="O32" s="1">
         <v>48345372262802.648</v>
@@ -2105,7 +2113,7 @@
         <v>2.4172686131401325E+17</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2121,42 +2129,42 @@
       <c r="E33">
         <v>228.49002075195313</v>
       </c>
-      <c r="F33" s="1">
-        <v>6520187849438040</v>
-      </c>
-      <c r="G33" s="1">
-        <v>2.0558774899461776E+17</v>
-      </c>
-      <c r="H33" s="1">
+      <c r="F33">
+        <v>2.0809175468136096E+17</v>
+      </c>
+      <c r="G33">
+        <v>2123840382175803.5</v>
+      </c>
+      <c r="H33">
         <v>2123840382.1758037</v>
       </c>
-      <c r="I33" s="1">
-        <v>21238403821758.035</v>
-      </c>
-      <c r="J33" s="1">
+      <c r="I33">
+        <v>2123840382175.8037</v>
+      </c>
+      <c r="J33">
         <v>941.22722840597055</v>
       </c>
-      <c r="K33" s="1">
-        <v>212384038217580.34</v>
-      </c>
-      <c r="L33" s="1">
+      <c r="K33">
+        <v>2123840382175803.5</v>
+      </c>
+      <c r="L33">
         <v>329.42952994208969</v>
       </c>
-      <c r="M33" s="1">
+      <c r="M33">
         <v>32.942952994208966</v>
       </c>
-      <c r="N33" s="1">
-        <v>0</v>
+      <c r="N33">
+        <v>418.45177513856993</v>
       </c>
       <c r="O33" s="1">
         <v>42476807643516.07</v>
       </c>
       <c r="P33" s="1">
         <f t="shared" si="0"/>
-        <v>2.1238403821758032E+17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2.1238403821758035E+17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2172,42 +2180,42 @@
       <c r="E34">
         <v>230.97369384765625</v>
       </c>
-      <c r="F34" s="1">
-        <v>5920322095900941</v>
-      </c>
-      <c r="G34" s="1">
-        <v>1.8667340897613482E+17</v>
-      </c>
-      <c r="H34" s="1">
+      <c r="F34">
+        <v>1.8894704288635488E+17</v>
+      </c>
+      <c r="G34">
+        <v>1928444307604698.5</v>
+      </c>
+      <c r="H34">
         <v>1928444307.6046987</v>
       </c>
-      <c r="I34" s="1">
-        <v>19284443076046.988</v>
-      </c>
-      <c r="J34" s="1">
+      <c r="I34">
+        <v>1928444307604.6987</v>
+      </c>
+      <c r="J34">
         <v>854.63310049813049</v>
       </c>
-      <c r="K34" s="1">
-        <v>192844430760469.88</v>
-      </c>
-      <c r="L34" s="1">
+      <c r="K34">
+        <v>1928444307604698.5</v>
+      </c>
+      <c r="L34">
         <v>299.12158517434563</v>
       </c>
-      <c r="M34" s="1">
+      <c r="M34">
         <v>29.912158517434566</v>
       </c>
-      <c r="N34" s="1">
-        <v>0</v>
+      <c r="N34">
+        <v>379.95366815012335</v>
       </c>
       <c r="O34" s="1">
         <v>38568886152093.977</v>
       </c>
       <c r="P34" s="1">
         <f t="shared" si="0"/>
-        <v>1.9284443076046986E+17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.9284443076046989E+17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2223,32 +2231,32 @@
       <c r="E35">
         <v>233.74447631835938</v>
       </c>
-      <c r="F35" s="1">
-        <v>5419733456911052</v>
-      </c>
-      <c r="G35" s="1">
-        <v>1.7088937117865315E+17</v>
-      </c>
-      <c r="H35" s="1">
+      <c r="F35">
+        <v>1.7297075958495606E+17</v>
+      </c>
+      <c r="G35">
+        <v>1765386065895177.3</v>
+      </c>
+      <c r="H35">
         <v>1765386065.8951774</v>
       </c>
-      <c r="I35" s="1">
-        <v>17653860658951.773</v>
-      </c>
-      <c r="J35" s="1">
+      <c r="I35">
+        <v>1765386065895.1775</v>
+      </c>
+      <c r="J35">
         <v>782.37020437795513</v>
       </c>
-      <c r="K35" s="1">
-        <v>176538606589517.72</v>
-      </c>
-      <c r="L35" s="1">
+      <c r="K35">
+        <v>1765386065895177.3</v>
+      </c>
+      <c r="L35">
         <v>273.82957153228426</v>
       </c>
-      <c r="M35" s="1">
+      <c r="M35">
         <v>27.382957153228428</v>
       </c>
-      <c r="N35" s="1">
-        <v>0</v>
+      <c r="N35">
+        <v>347.82695501906323</v>
       </c>
       <c r="O35" s="1">
         <v>35307721317903.547</v>
@@ -2258,7 +2266,7 @@
         <v>1.765386065895177E+17</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2274,42 +2282,42 @@
       <c r="E36">
         <v>236.51438903808594</v>
       </c>
-      <c r="F36" s="1">
-        <v>4971659691391776</v>
-      </c>
-      <c r="G36" s="1">
-        <v>1.5676117748794688E+17</v>
-      </c>
-      <c r="H36" s="1">
+      <c r="F36">
+        <v>1.5867048814390746E+17</v>
+      </c>
+      <c r="G36">
+        <v>1619433651734988.5</v>
+      </c>
+      <c r="H36">
         <v>1619433651.7349885</v>
       </c>
-      <c r="I36" s="1">
-        <v>16194336517349.885</v>
-      </c>
-      <c r="J36" s="1">
+      <c r="I36">
+        <v>1619433651734.9885</v>
+      </c>
+      <c r="J36">
         <v>717.68813720753087</v>
       </c>
-      <c r="K36" s="1">
-        <v>161943365173498.84</v>
-      </c>
-      <c r="L36" s="1">
+      <c r="K36">
+        <v>1619433651734988.5</v>
+      </c>
+      <c r="L36">
         <v>251.19084802263581</v>
       </c>
-      <c r="M36" s="1">
+      <c r="M36">
         <v>25.119084802263579</v>
       </c>
-      <c r="N36" s="1">
-        <v>0</v>
+      <c r="N36">
+        <v>319.0705346667379</v>
       </c>
       <c r="O36" s="1">
         <v>32388673034699.77</v>
       </c>
       <c r="P36" s="1">
         <f t="shared" si="0"/>
-        <v>1.6194336517349885E+17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.6194336517349882E+17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2325,42 +2333,42 @@
       <c r="E37">
         <v>239.28343200683594</v>
       </c>
-      <c r="F37" s="1">
-        <v>4569665222434110</v>
-      </c>
-      <c r="G37" s="1">
-        <v>1.4408590801876798E+17</v>
-      </c>
-      <c r="H37" s="1">
+      <c r="F37">
+        <v>1.4584083716616576E+17</v>
+      </c>
+      <c r="G37">
+        <v>1488490785317851.3</v>
+      </c>
+      <c r="H37">
         <v>1488490785.3178513</v>
       </c>
-      <c r="I37" s="1">
-        <v>14884907853178.514</v>
-      </c>
-      <c r="J37" s="1">
+      <c r="I37">
+        <v>1488490785317.8513</v>
+      </c>
+      <c r="J37">
         <v>659.65788584227857</v>
       </c>
-      <c r="K37" s="1">
-        <v>148849078531785.13</v>
-      </c>
-      <c r="L37" s="1">
+      <c r="K37">
+        <v>1488490785317851.3</v>
+      </c>
+      <c r="L37">
         <v>230.8802600447975</v>
       </c>
-      <c r="M37" s="1">
+      <c r="M37">
         <v>23.088026004479751</v>
       </c>
-      <c r="N37" s="1">
-        <v>0</v>
+      <c r="N37">
+        <v>293.27138546803496</v>
       </c>
       <c r="O37" s="1">
         <v>29769815706357.027</v>
       </c>
       <c r="P37" s="1">
         <f t="shared" si="0"/>
-        <v>1.4884907853178512E+17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.4884907853178515E+17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2376,42 +2384,42 @@
       <c r="E38">
         <v>242.05162048339844</v>
       </c>
-      <c r="F38" s="1">
-        <v>4208207543075235.5</v>
-      </c>
-      <c r="G38" s="1">
-        <v>1.3268880223406056E+17</v>
-      </c>
-      <c r="H38" s="1">
+      <c r="F38">
+        <v>1.3430491757646808E+17</v>
+      </c>
+      <c r="G38">
+        <v>1370752089194840.5</v>
+      </c>
+      <c r="H38">
         <v>1370752089.1948404</v>
       </c>
-      <c r="I38" s="1">
-        <v>13707520891948.406</v>
-      </c>
-      <c r="J38" s="1">
+      <c r="I38">
+        <v>1370752089194.8406</v>
+      </c>
+      <c r="J38">
         <v>607.47935700459641</v>
       </c>
-      <c r="K38" s="1">
-        <v>137075208919484.05</v>
-      </c>
-      <c r="L38" s="1">
+      <c r="K38">
+        <v>1370752089194840.5</v>
+      </c>
+      <c r="L38">
         <v>212.61777495160874</v>
       </c>
-      <c r="M38" s="1">
+      <c r="M38">
         <v>21.261777495160874</v>
       </c>
-      <c r="N38" s="1">
-        <v>0</v>
+      <c r="N38">
+        <v>270.07380112570269</v>
       </c>
       <c r="O38" s="1">
         <v>27415041783896.813</v>
       </c>
       <c r="P38" s="1">
         <f t="shared" si="0"/>
-        <v>1.3707520891948406E+17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.3707520891948408E+17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2427,42 +2435,42 @@
       <c r="E39">
         <v>244.81892395019531</v>
       </c>
-      <c r="F39" s="1">
-        <v>3882494800667557</v>
-      </c>
-      <c r="G39" s="1">
-        <v>1.2241876844412462E+17</v>
-      </c>
-      <c r="H39" s="1">
+      <c r="F39">
+        <v>1.2390979742735557E+17</v>
+      </c>
+      <c r="G39">
+        <v>1264656698802940.3</v>
+      </c>
+      <c r="H39">
         <v>1264656698.8029404</v>
       </c>
-      <c r="I39" s="1">
-        <v>12646566988029.404</v>
-      </c>
-      <c r="J39" s="1">
+      <c r="I39">
+        <v>1264656698802.9404</v>
+      </c>
+      <c r="J39">
         <v>560.46081875507195</v>
       </c>
-      <c r="K39" s="1">
-        <v>126465669880294.03</v>
-      </c>
-      <c r="L39" s="1">
+      <c r="K39">
+        <v>1264656698802940.3</v>
+      </c>
+      <c r="L39">
         <v>196.16128656427517</v>
       </c>
-      <c r="M39" s="1">
+      <c r="M39">
         <v>19.616128656427517</v>
       </c>
-      <c r="N39" s="1">
-        <v>0</v>
+      <c r="N39">
+        <v>249.17025073834813</v>
       </c>
       <c r="O39" s="1">
         <v>25293133976058.809</v>
       </c>
       <c r="P39" s="1">
         <f t="shared" si="0"/>
-        <v>1.2646566988029403E+17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.2646566988029405E+17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2478,32 +2486,32 @@
       <c r="E40">
         <v>247.58538818359375</v>
       </c>
-      <c r="F40" s="1">
-        <v>3588382920893457</v>
-      </c>
-      <c r="G40" s="1">
-        <v>1.1314514002856534E+17</v>
-      </c>
-      <c r="H40" s="1">
+      <c r="F40">
+        <v>1.1452321861274352E+17</v>
+      </c>
+      <c r="G40">
+        <v>1168854752361212.3</v>
+      </c>
+      <c r="H40">
         <v>1168854752.3612123</v>
       </c>
-      <c r="I40" s="1">
-        <v>11688547523612.123</v>
-      </c>
-      <c r="J40" s="1">
+      <c r="I40">
+        <v>1168854752361.2124</v>
+      </c>
+      <c r="J40">
         <v>518.00404974267224</v>
       </c>
-      <c r="K40" s="1">
-        <v>116885475236121.23</v>
-      </c>
-      <c r="L40" s="1">
+      <c r="K40">
+        <v>1168854752361212.3</v>
+      </c>
+      <c r="L40">
         <v>181.30141740993525</v>
       </c>
-      <c r="M40" s="1">
+      <c r="M40">
         <v>18.130141740993526</v>
       </c>
-      <c r="N40" s="1">
-        <v>0</v>
+      <c r="N40">
+        <v>230.29477643872025</v>
       </c>
       <c r="O40" s="1">
         <v>23377095047224.246</v>
@@ -2513,7 +2521,7 @@
         <v>1.1688547523612123E+17</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2529,32 +2537,32 @@
       <c r="E41">
         <v>250.35098266601563</v>
       </c>
-      <c r="F41" s="1">
-        <v>3322267114706579.5</v>
-      </c>
-      <c r="G41" s="1">
-        <v>1.0475425454655222E+17</v>
-      </c>
-      <c r="H41" s="1">
+      <c r="F41">
+        <v>1.0603013431262707E+17</v>
+      </c>
+      <c r="G41">
+        <v>1082172051100746.1</v>
+      </c>
+      <c r="H41">
         <v>1082172051.1007462</v>
       </c>
-      <c r="I41" s="1">
-        <v>10821720511007.461</v>
-      </c>
-      <c r="J41" s="1">
+      <c r="I41">
+        <v>1082172051100.7462</v>
+      </c>
+      <c r="J41">
         <v>479.58867759754565</v>
       </c>
-      <c r="K41" s="1">
-        <v>108217205110074.61</v>
-      </c>
-      <c r="L41" s="1">
+      <c r="K41">
+        <v>1082172051100746.1</v>
+      </c>
+      <c r="L41">
         <v>167.85603715914095</v>
       </c>
-      <c r="M41" s="1">
+      <c r="M41">
         <v>16.785603715914096</v>
       </c>
-      <c r="N41" s="1">
-        <v>0</v>
+      <c r="N41">
+        <v>213.21603054017561</v>
       </c>
       <c r="O41" s="1">
         <v>21643441022014.922</v>
@@ -2564,7 +2572,7 @@
         <v>1.0821720511007461E+17</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2580,42 +2588,42 @@
       <c r="E42">
         <v>253.11570739746094</v>
       </c>
-      <c r="F42" s="1">
-        <v>3081011525904070.5</v>
-      </c>
-      <c r="G42" s="1">
-        <v>9.7147235457592416E+16</v>
-      </c>
-      <c r="H42" s="1">
+      <c r="F42">
+        <v>9.8330463695786496E+16</v>
+      </c>
+      <c r="G42">
+        <v>1003587143156946.4</v>
+      </c>
+      <c r="H42">
         <v>1003587143.1569464</v>
       </c>
-      <c r="I42" s="1">
-        <v>10035871431569.465</v>
-      </c>
-      <c r="J42" s="1">
+      <c r="I42">
+        <v>1003587143156.9465</v>
+      </c>
+      <c r="J42">
         <v>444.76202314684491</v>
       </c>
-      <c r="K42" s="1">
-        <v>100358714315694.64</v>
-      </c>
-      <c r="L42" s="1">
+      <c r="K42">
+        <v>1003587143156946.4</v>
+      </c>
+      <c r="L42">
         <v>155.6667081013957</v>
       </c>
-      <c r="M42" s="1">
+      <c r="M42">
         <v>15.56667081013957</v>
       </c>
-      <c r="N42" s="1">
-        <v>0</v>
+      <c r="N42">
+        <v>197.73276046764053</v>
       </c>
       <c r="O42" s="1">
         <v>20071742863138.93</v>
       </c>
       <c r="P42" s="1">
         <f t="shared" si="0"/>
-        <v>1.0035871431569464E+17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.0035871431569462E+17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2631,32 +2639,32 @@
       <c r="E43">
         <v>255.87957763671875</v>
       </c>
-      <c r="F43" s="1">
-        <v>2861880419983107</v>
-      </c>
-      <c r="G43" s="1">
-        <v>9.0237822440469776E+16</v>
-      </c>
-      <c r="H43" s="1">
+      <c r="F43">
+        <v>9.13368958125712E+16</v>
+      </c>
+      <c r="G43">
+        <v>932208909508985.25</v>
+      </c>
+      <c r="H43">
         <v>932208909.50898528</v>
       </c>
-      <c r="I43" s="1">
-        <v>9322089095089.8535</v>
-      </c>
-      <c r="J43" s="1">
+      <c r="I43">
+        <v>932208909508.98535</v>
+      </c>
+      <c r="J43">
         <v>413.12916712394673</v>
       </c>
-      <c r="K43" s="1">
-        <v>93220890950898.531</v>
-      </c>
-      <c r="L43" s="1">
+      <c r="K43">
+        <v>932208909508985.25</v>
+      </c>
+      <c r="L43">
         <v>144.59520849338134</v>
       </c>
-      <c r="M43" s="1">
+      <c r="M43">
         <v>14.459520849338135</v>
       </c>
-      <c r="N43" s="1">
-        <v>0</v>
+      <c r="N43">
+        <v>183.66939260491736</v>
       </c>
       <c r="O43" s="1">
         <v>18644178190179.707</v>
@@ -2666,7 +2674,7 @@
         <v>9.3220890950898528E+16</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2682,42 +2690,42 @@
       <c r="E44">
         <v>258.642578125</v>
       </c>
-      <c r="F44" s="1">
-        <v>2662478713665614.5</v>
-      </c>
-      <c r="G44" s="1">
-        <v>8.3950496232370976E+16</v>
-      </c>
-      <c r="H44" s="1">
+      <c r="F44">
+        <v>8.4972991595050736E+16</v>
+      </c>
+      <c r="G44">
+        <v>867257192483171.25</v>
+      </c>
+      <c r="H44">
         <v>867257192.48317122</v>
       </c>
-      <c r="I44" s="1">
-        <v>8672571924831.7129</v>
-      </c>
-      <c r="J44" s="1">
+      <c r="I44">
+        <v>867257192483.17126</v>
+      </c>
+      <c r="J44">
         <v>384.34436525772276</v>
       </c>
-      <c r="K44" s="1">
-        <v>86725719248317.125</v>
-      </c>
-      <c r="L44" s="1">
+      <c r="K44">
+        <v>867257192483171.25</v>
+      </c>
+      <c r="L44">
         <v>134.52052784020296</v>
       </c>
-      <c r="M44" s="1">
+      <c r="M44">
         <v>13.452052784020296</v>
       </c>
-      <c r="N44" s="1">
-        <v>0</v>
+      <c r="N44">
+        <v>170.87221560618931</v>
       </c>
       <c r="O44" s="1">
         <v>17345143849663.426</v>
       </c>
       <c r="P44" s="1">
         <f t="shared" si="0"/>
-        <v>8.6725719248317136E+16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8.672571924831712E+16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2733,32 +2741,32 @@
       <c r="E45">
         <v>261.40469360351563</v>
       </c>
-      <c r="F45" s="1">
-        <v>2480706561836997</v>
-      </c>
-      <c r="G45" s="1">
-        <v>7.8219046711698928E+16</v>
-      </c>
-      <c r="H45" s="1">
+      <c r="F45">
+        <v>7.9171734499446688E+16</v>
+      </c>
+      <c r="G45">
+        <v>808048003220030.25</v>
+      </c>
+      <c r="H45">
         <v>808048003.22003031</v>
       </c>
-      <c r="I45" s="1">
-        <v>8080480032200.3027</v>
-      </c>
-      <c r="J45" s="1">
+      <c r="I45">
+        <v>808048003220.03027</v>
+      </c>
+      <c r="J45">
         <v>358.10449263169335</v>
       </c>
-      <c r="K45" s="1">
-        <v>80804800322003.031</v>
-      </c>
-      <c r="L45" s="1">
+      <c r="K45">
+        <v>808048003220030.25</v>
+      </c>
+      <c r="L45">
         <v>125.33657242109267</v>
       </c>
-      <c r="M45" s="1">
+      <c r="M45">
         <v>12.533657242109266</v>
       </c>
-      <c r="N45" s="1">
-        <v>0</v>
+      <c r="N45">
+        <v>159.20646588242968</v>
       </c>
       <c r="O45" s="1">
         <v>16160960064400.605</v>
@@ -2768,7 +2776,7 @@
         <v>8.0804800322003024E+16</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2784,42 +2792,42 @@
       <c r="E46">
         <v>264.16598510742188</v>
       </c>
-      <c r="F46" s="1">
-        <v>2314722745117498.5</v>
-      </c>
-      <c r="G46" s="1">
-        <v>7.2985418473236752E+16</v>
-      </c>
-      <c r="H46" s="1">
+      <c r="F46">
+        <v>7.3874362020700272E+16</v>
+      </c>
+      <c r="G46">
+        <v>753981595797900.38</v>
+      </c>
+      <c r="H46">
         <v>753981595.79790032</v>
       </c>
-      <c r="I46" s="1">
-        <v>7539815957979.0039</v>
-      </c>
-      <c r="J46" s="1">
+      <c r="I46">
+        <v>753981595797.90039</v>
+      </c>
+      <c r="J46">
         <v>334.14375846594334</v>
       </c>
-      <c r="K46" s="1">
-        <v>75398159579790.031</v>
-      </c>
-      <c r="L46" s="1">
+      <c r="K46">
+        <v>753981595797900.38</v>
+      </c>
+      <c r="L46">
         <v>116.95031546308016</v>
       </c>
-      <c r="M46" s="1">
+      <c r="M46">
         <v>11.695031546308016</v>
       </c>
-      <c r="N46" s="1">
-        <v>0</v>
+      <c r="N46">
+        <v>148.55397789367711</v>
       </c>
       <c r="O46" s="1">
         <v>15079631915958.008</v>
       </c>
       <c r="P46" s="1">
         <f t="shared" si="0"/>
-        <v>7.5398159579790048E+16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+        <v>7.5398159579790032E+16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2835,42 +2843,42 @@
       <c r="E47">
         <v>266.9263916015625</v>
       </c>
-      <c r="F47" s="1">
-        <v>2162899528546733.5</v>
-      </c>
-      <c r="G47" s="1">
-        <v>6.8198287479365744E+16</v>
-      </c>
-      <c r="H47" s="1">
+      <c r="F47">
+        <v>6.9028925007669776E+16</v>
+      </c>
+      <c r="G47">
+        <v>704527763216588.38</v>
+      </c>
+      <c r="H47">
         <v>704527763.21658838</v>
       </c>
-      <c r="I47" s="1">
-        <v>7045277632165.8838</v>
-      </c>
-      <c r="J47" s="1">
+      <c r="I47">
+        <v>704527763216.58838</v>
+      </c>
+      <c r="J47">
         <v>312.22718970437046</v>
       </c>
-      <c r="K47" s="1">
-        <v>70452776321658.828</v>
-      </c>
-      <c r="L47" s="1">
+      <c r="K47">
+        <v>704527763216588.38</v>
+      </c>
+      <c r="L47">
         <v>109.27951639652966</v>
       </c>
-      <c r="M47" s="1">
+      <c r="M47">
         <v>10.927951639652965</v>
       </c>
-      <c r="N47" s="1">
-        <v>0</v>
+      <c r="N47">
+        <v>138.81028707551155</v>
       </c>
       <c r="O47" s="1">
         <v>14090555264331.768</v>
       </c>
       <c r="P47" s="1">
         <f t="shared" si="0"/>
-        <v>7.0452776321658824E+16</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+        <v>7.0452776321658832E+16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2886,42 +2894,42 @@
       <c r="E48">
         <v>269.68597412109375</v>
       </c>
-      <c r="F48" s="1">
-        <v>2023806301903883</v>
-      </c>
-      <c r="G48" s="1">
-        <v>6.3812545223739408E+16</v>
-      </c>
-      <c r="H48" s="1">
+      <c r="F48">
+        <v>6.4589765544051312E+16</v>
+      </c>
+      <c r="G48">
+        <v>659220508509704.63</v>
+      </c>
+      <c r="H48">
         <v>659220508.50970471</v>
       </c>
-      <c r="I48" s="1">
-        <v>6592205085097.0469</v>
-      </c>
-      <c r="J48" s="1">
+      <c r="I48">
+        <v>659220508509.70471</v>
+      </c>
+      <c r="J48">
         <v>292.14826939927877</v>
       </c>
-      <c r="K48" s="1">
-        <v>65922050850970.469</v>
-      </c>
-      <c r="L48" s="1">
+      <c r="K48">
+        <v>659220508509704.63</v>
+      </c>
+      <c r="L48">
         <v>102.25189428974755</v>
       </c>
-      <c r="M48" s="1">
+      <c r="M48">
         <v>10.225189428974756</v>
       </c>
-      <c r="N48" s="1">
-        <v>0</v>
+      <c r="N48">
+        <v>129.88357990963308</v>
       </c>
       <c r="O48" s="1">
         <v>13184410170194.094</v>
       </c>
       <c r="P48" s="1">
         <f t="shared" si="0"/>
-        <v>6.5922050850970464E+16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+        <v>6.5922050850970472E+16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2937,32 +2945,32 @@
       <c r="E49">
         <v>270.64999389648438</v>
       </c>
-      <c r="F49" s="1">
-        <v>1821944663634604.3</v>
-      </c>
-      <c r="G49" s="1">
-        <v>5.7447655012221408E+16</v>
-      </c>
-      <c r="H49" s="1">
+      <c r="F49">
+        <v>5.8147352613582024E+16</v>
+      </c>
+      <c r="G49">
+        <v>593467510456832.75</v>
+      </c>
+      <c r="H49">
         <v>593467510.45683277</v>
       </c>
-      <c r="I49" s="1">
-        <v>5934675104568.3271</v>
-      </c>
-      <c r="J49" s="1">
+      <c r="I49">
+        <v>593467510456.83276</v>
+      </c>
+      <c r="J49">
         <v>263.00836197681741</v>
       </c>
-      <c r="K49" s="1">
-        <v>59346751045683.273</v>
-      </c>
-      <c r="L49" s="1">
+      <c r="K49">
+        <v>593467510456832.75</v>
+      </c>
+      <c r="L49">
         <v>92.0529266918861</v>
       </c>
-      <c r="M49" s="1">
+      <c r="M49">
         <v>9.2052926691886103</v>
       </c>
-      <c r="N49" s="1">
-        <v>0</v>
+      <c r="N49">
+        <v>116.92852971526793</v>
       </c>
       <c r="O49" s="1">
         <v>11869350209136.654</v>
@@ -2972,7 +2980,7 @@
         <v>5.934675104568328E+16</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2988,42 +2996,42 @@
       <c r="E50">
         <v>270.64999389648438</v>
       </c>
-      <c r="F50" s="1">
-        <v>1605781681402194</v>
-      </c>
-      <c r="G50" s="1">
-        <v>5.0631829769248536E+16</v>
-      </c>
-      <c r="H50" s="1">
+      <c r="F50">
+        <v>5.1248512379435248E+16</v>
+      </c>
+      <c r="G50">
+        <v>523056092657526.25</v>
+      </c>
+      <c r="H50">
         <v>523056092.65752625</v>
       </c>
-      <c r="I50" s="1">
-        <v>5230560926575.2627</v>
-      </c>
-      <c r="J50" s="1">
+      <c r="I50">
+        <v>523056092657.52631</v>
+      </c>
+      <c r="J50">
         <v>231.80397195788322</v>
       </c>
-      <c r="K50" s="1">
-        <v>52305609265752.625</v>
-      </c>
-      <c r="L50" s="1">
+      <c r="K50">
+        <v>523056092657526.25</v>
+      </c>
+      <c r="L50">
         <v>81.131390185259121</v>
       </c>
-      <c r="M50" s="1">
+      <c r="M50">
         <v>8.1131390185259118</v>
       </c>
-      <c r="N50" s="1">
-        <v>0</v>
+      <c r="N50">
+        <v>103.05564971194177</v>
       </c>
       <c r="O50" s="1">
         <v>10461121853150.525</v>
       </c>
       <c r="P50" s="1">
         <f t="shared" si="0"/>
-        <v>5.2305609265752624E+16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+        <v>5.2305609265752632E+16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3039,42 +3047,42 @@
       <c r="E51">
         <v>270.64999389648438</v>
       </c>
-      <c r="F51" s="1">
-        <v>1415265161337517.8</v>
-      </c>
-      <c r="G51" s="1">
-        <v>4.4624661968130584E+16</v>
-      </c>
-      <c r="H51" s="1">
+      <c r="F51">
+        <v>4.5168178825937688E+16</v>
+      </c>
+      <c r="G51">
+        <v>460998574050935.75</v>
+      </c>
+      <c r="H51">
         <v>460998574.05093575</v>
       </c>
-      <c r="I51" s="1">
-        <v>4609985740509.3574</v>
-      </c>
-      <c r="J51" s="1">
+      <c r="I51">
+        <v>460998574050.93579</v>
+      </c>
+      <c r="J51">
         <v>204.30179866367652</v>
       </c>
-      <c r="K51" s="1">
-        <v>46099857405093.578</v>
-      </c>
-      <c r="L51" s="1">
+      <c r="K51">
+        <v>460998574050935.75</v>
+      </c>
+      <c r="L51">
         <v>71.505629532286775</v>
       </c>
-      <c r="M51" s="1">
+      <c r="M51">
         <v>7.1505629532286781</v>
       </c>
-      <c r="N51" s="1">
-        <v>0</v>
+      <c r="N51">
+        <v>90.828705050959684</v>
       </c>
       <c r="O51" s="1">
         <v>9219971481018.7148</v>
       </c>
       <c r="P51" s="1">
         <f t="shared" si="0"/>
-        <v>4.6099857405093592E+16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+        <v>4.6099857405093576E+16</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3090,32 +3098,32 @@
       <c r="E52">
         <v>270.64999389648438</v>
       </c>
-      <c r="F52" s="1">
-        <v>1247352302055582.3</v>
-      </c>
-      <c r="G52" s="1">
-        <v>3.9330209175639576E+16</v>
-      </c>
-      <c r="H52" s="1">
+      <c r="F52">
+        <v>3.9809240965803192E+16</v>
+      </c>
+      <c r="G52">
+        <v>406303813797929.5</v>
+      </c>
+      <c r="H52">
         <v>406303813.79792953</v>
       </c>
-      <c r="I52" s="1">
-        <v>4063038137979.2954</v>
-      </c>
-      <c r="J52" s="1">
+      <c r="I52">
+        <v>406303813797.92957</v>
+      </c>
+      <c r="J52">
         <v>180.06259592824009</v>
       </c>
-      <c r="K52" s="1">
-        <v>40630381379792.953</v>
-      </c>
-      <c r="L52" s="1">
+      <c r="K52">
+        <v>406303813797929.5</v>
+      </c>
+      <c r="L52">
         <v>63.02190857488403</v>
       </c>
-      <c r="M52" s="1">
+      <c r="M52">
         <v>6.3021908574884034</v>
       </c>
-      <c r="N52" s="1">
-        <v>0</v>
+      <c r="N52">
+        <v>80.05241521735087</v>
       </c>
       <c r="O52" s="1">
         <v>8126076275958.5908</v>
@@ -3125,7 +3133,7 @@
         <v>4.063038137979296E+16</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>52</v>
       </c>
@@ -3141,32 +3149,32 @@
       <c r="E53">
         <v>269.02914428710938</v>
       </c>
-      <c r="F53" s="1">
-        <v>1056712629033666.1</v>
-      </c>
-      <c r="G53" s="1">
-        <v>3.3319158244181576E+16</v>
-      </c>
-      <c r="H53" s="1">
+      <c r="F53">
+        <v>3.3724976986440924E+16</v>
+      </c>
+      <c r="G53">
+        <v>344206180208487.38</v>
+      </c>
+      <c r="H53">
         <v>344206180.20848739</v>
       </c>
-      <c r="I53" s="1">
-        <v>3442061802084.8735</v>
-      </c>
-      <c r="J53" s="1">
+      <c r="I53">
+        <v>344206180208.48737</v>
+      </c>
+      <c r="J53">
         <v>152.54264478479203</v>
       </c>
-      <c r="K53" s="1">
-        <v>34420618020848.738</v>
-      </c>
-      <c r="L53" s="1">
+      <c r="K53">
+        <v>344206180208487.38</v>
+      </c>
+      <c r="L53">
         <v>53.389925674677215</v>
       </c>
-      <c r="M53" s="1">
+      <c r="M53">
         <v>5.3389925674677219</v>
       </c>
-      <c r="N53" s="1">
-        <v>0</v>
+      <c r="N53">
+        <v>67.817566861757442</v>
       </c>
       <c r="O53" s="1">
         <v>6884123604169.7471</v>
@@ -3176,7 +3184,7 @@
         <v>3.4420618020848732E+16</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3192,42 +3200,42 @@
       <c r="E54">
         <v>266.27471923828125</v>
       </c>
-      <c r="F54" s="1">
-        <v>868012385456072</v>
-      </c>
-      <c r="G54" s="1">
-        <v>2.736925937505662E+16</v>
-      </c>
-      <c r="H54" s="1">
+      <c r="F54">
+        <v>2.7702609885737512E+16</v>
+      </c>
+      <c r="G54">
+        <v>282740282800171.75</v>
+      </c>
+      <c r="H54">
         <v>282740282.80017173</v>
       </c>
-      <c r="I54" s="1">
-        <v>2827402828001.7173</v>
-      </c>
-      <c r="J54" s="1">
+      <c r="I54">
+        <v>282740282800.17175</v>
+      </c>
+      <c r="J54">
         <v>125.30266161814474</v>
       </c>
-      <c r="K54" s="1">
-        <v>28274028280017.172</v>
-      </c>
-      <c r="L54" s="1">
+      <c r="K54">
+        <v>282740282800171.75</v>
+      </c>
+      <c r="L54">
         <v>43.855931566350655</v>
       </c>
-      <c r="M54" s="1">
+      <c r="M54">
         <v>4.3855931566350659</v>
       </c>
-      <c r="N54" s="1">
-        <v>0</v>
+      <c r="N54">
+        <v>55.70718695898664</v>
       </c>
       <c r="O54" s="1">
         <v>5654805656003.4346</v>
       </c>
       <c r="P54" s="1">
         <f t="shared" si="0"/>
-        <v>2.8274028280017168E+16</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2.8274028280017172E+16</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3243,42 +3251,42 @@
       <c r="E55">
         <v>263.52117919921875</v>
       </c>
-      <c r="F55" s="1">
-        <v>710099556483803</v>
-      </c>
-      <c r="G55" s="1">
-        <v>2.2390117087219176E+16</v>
-      </c>
-      <c r="H55" s="1">
+      <c r="F55">
+        <v>2.2662822930769756E+16</v>
+      </c>
+      <c r="G55">
+        <v>231302862471272.5</v>
+      </c>
+      <c r="H55">
         <v>231302862.4712725</v>
       </c>
-      <c r="I55" s="1">
-        <v>2313028624712.7251</v>
-      </c>
-      <c r="J55" s="1">
+      <c r="I55">
+        <v>231302862471.27249</v>
+      </c>
+      <c r="J55">
         <v>102.50702171091032</v>
       </c>
-      <c r="K55" s="1">
-        <v>23130286247127.25</v>
-      </c>
-      <c r="L55" s="1">
+      <c r="K55">
+        <v>231302862471272.5</v>
+      </c>
+      <c r="L55">
         <v>35.877457598818609</v>
       </c>
-      <c r="M55" s="1">
+      <c r="M55">
         <v>3.5877457598818614</v>
       </c>
-      <c r="N55" s="1">
-        <v>0</v>
+      <c r="N55">
+        <v>45.572677781264936</v>
       </c>
       <c r="O55" s="1">
         <v>4626057249425.4502</v>
       </c>
       <c r="P55" s="1">
         <f t="shared" si="0"/>
-        <v>2.3130286247127252E+16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2.3130286247127248E+16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3294,42 +3302,42 @@
       <c r="E56">
         <v>260.76849365234375</v>
       </c>
-      <c r="F56" s="1">
-        <v>578470380415801.63</v>
-      </c>
-      <c r="G56" s="1">
-        <v>1.8239723473610484E+16</v>
-      </c>
-      <c r="H56" s="1">
+      <c r="F56">
+        <v>1.8461878594846524E+16</v>
+      </c>
+      <c r="G56">
+        <v>188426895388538.09</v>
+      </c>
+      <c r="H56">
         <v>188426895.38853809</v>
       </c>
-      <c r="I56" s="1">
-        <v>1884268953885.3809</v>
-      </c>
-      <c r="J56" s="1">
+      <c r="I56">
+        <v>188426895388.53809</v>
+      </c>
+      <c r="J56">
         <v>83.505580735781905</v>
       </c>
-      <c r="K56" s="1">
-        <v>18842689538853.809</v>
-      </c>
-      <c r="L56" s="1">
+      <c r="K56">
+        <v>188426895388538.09</v>
+      </c>
+      <c r="L56">
         <v>29.226953257523665</v>
       </c>
-      <c r="M56" s="1">
+      <c r="M56">
         <v>2.9226953257523665</v>
       </c>
-      <c r="N56" s="1">
-        <v>0</v>
+      <c r="N56">
+        <v>37.124997490822111</v>
       </c>
       <c r="O56" s="1">
         <v>3768537907770.7617</v>
       </c>
       <c r="P56" s="1">
         <f t="shared" si="0"/>
-        <v>1.8842689538853804E+16</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.8842689538853812E+16</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3345,42 +3353,42 @@
       <c r="E57">
         <v>258.01666259765625</v>
       </c>
-      <c r="F57" s="1">
-        <v>469195507834665.75</v>
-      </c>
-      <c r="G57" s="1">
-        <v>1.4794182394979498E+16</v>
-      </c>
-      <c r="H57" s="1">
+      <c r="F57">
+        <v>1.4974371715738654E+16</v>
+      </c>
+      <c r="G57">
+        <v>152832462758052.66</v>
+      </c>
+      <c r="H57">
         <v>152832462.75805268</v>
       </c>
-      <c r="I57" s="1">
-        <v>1528324627580.5266</v>
-      </c>
-      <c r="J57" s="1">
+      <c r="I57">
+        <v>152832462758.05267</v>
+      </c>
+      <c r="J57">
         <v>67.731114136200304</v>
       </c>
-      <c r="K57" s="1">
-        <v>15283246275805.266</v>
-      </c>
-      <c r="L57" s="1">
+      <c r="K57">
+        <v>152832462758052.66</v>
+      </c>
+      <c r="L57">
         <v>23.705889947670105</v>
       </c>
-      <c r="M57" s="1">
+      <c r="M57">
         <v>2.3705889947670102</v>
       </c>
-      <c r="N57" s="1">
-        <v>0</v>
+      <c r="N57">
+        <v>30.111968807368086</v>
       </c>
       <c r="O57" s="1">
         <v>3056649255161.0532</v>
       </c>
       <c r="P57" s="1">
         <f t="shared" si="0"/>
-        <v>1.5283246275805268E+16</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1.5283246275805264E+16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3396,32 +3404,32 @@
       <c r="E58">
         <v>255.26568603515625</v>
       </c>
-      <c r="F58" s="1">
-        <v>378858655833858.88</v>
-      </c>
-      <c r="G58" s="1">
-        <v>1.194577518908795E+16</v>
-      </c>
-      <c r="H58" s="1">
+      <c r="F58">
+        <v>1.209127164572173E+16</v>
+      </c>
+      <c r="G58">
+        <v>123406768482313.55</v>
+      </c>
+      <c r="H58">
         <v>123406768.48231354</v>
       </c>
-      <c r="I58" s="1">
-        <v>1234067684823.1355</v>
-      </c>
-      <c r="J58" s="1">
+      <c r="I58">
+        <v>123406768482.31355</v>
+      </c>
+      <c r="J58">
         <v>54.690461505468484</v>
       </c>
-      <c r="K58" s="1">
-        <v>12340676848231.354</v>
-      </c>
-      <c r="L58" s="1">
+      <c r="K58">
+        <v>123406768482313.55</v>
+      </c>
+      <c r="L58">
         <v>19.141661526913968</v>
       </c>
-      <c r="M58" s="1">
+      <c r="M58">
         <v>1.9141661526913969</v>
       </c>
-      <c r="N58" s="1">
-        <v>0</v>
+      <c r="N58">
+        <v>24.314341966996309</v>
       </c>
       <c r="O58" s="1">
         <v>2468135369646.271</v>
@@ -3431,7 +3439,7 @@
         <v>1.2340676848231354E+16</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3447,42 +3455,42 @@
       <c r="E59">
         <v>252.51556396484375</v>
       </c>
-      <c r="F59" s="1">
-        <v>304500818941774</v>
-      </c>
-      <c r="G59" s="1">
-        <v>9601201587873342</v>
-      </c>
-      <c r="H59" s="1">
+      <c r="F59">
+        <v>9718141743564390</v>
+      </c>
+      <c r="G59">
+        <v>99185966816873.375</v>
+      </c>
+      <c r="H59">
         <v>99185966.816873387</v>
       </c>
-      <c r="I59" s="1">
-        <v>991859668168.73389</v>
-      </c>
-      <c r="J59" s="1">
+      <c r="I59">
+        <v>99185966816.873383</v>
+      </c>
+      <c r="J59">
         <v>43.956473107537228</v>
       </c>
-      <c r="K59" s="1">
-        <v>9918596681687.3379</v>
-      </c>
-      <c r="L59" s="1">
+      <c r="K59">
+        <v>99185966816873.375</v>
+      </c>
+      <c r="L59">
         <v>15.384765587638029</v>
       </c>
-      <c r="M59" s="1">
+      <c r="M59">
         <v>1.538476558763803</v>
       </c>
-      <c r="N59" s="1">
-        <v>0</v>
+      <c r="N59">
+        <v>19.542214298061296</v>
       </c>
       <c r="O59" s="1">
         <v>1983719336337.4678</v>
       </c>
       <c r="P59" s="1">
         <f t="shared" si="0"/>
-        <v>9918596681687338</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+        <v>9918596681687340</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3498,42 +3506,42 @@
       <c r="E60">
         <v>249.76629638671875</v>
       </c>
-      <c r="F60" s="1">
-        <v>243569052719991.81</v>
-      </c>
-      <c r="G60" s="1">
-        <v>7679964815395669</v>
-      </c>
-      <c r="H60" s="1">
+      <c r="F60">
+        <v>7773504803385136</v>
+      </c>
+      <c r="G60">
+        <v>79338479497889.141</v>
+      </c>
+      <c r="H60">
         <v>79338479.497889146</v>
       </c>
-      <c r="I60" s="1">
-        <v>793384794978.89148</v>
-      </c>
-      <c r="J60" s="1">
+      <c r="I60">
+        <v>79338479497.889145</v>
+      </c>
+      <c r="J60">
         <v>35.160616490039388</v>
       </c>
-      <c r="K60" s="1">
-        <v>7933847949788.9141</v>
-      </c>
-      <c r="L60" s="1">
+      <c r="K60">
+        <v>79338479497889.141</v>
+      </c>
+      <c r="L60">
         <v>12.306215771513784</v>
       </c>
-      <c r="M60" s="1">
+      <c r="M60">
         <v>1.2306215771513784</v>
       </c>
-      <c r="N60" s="1">
-        <v>0</v>
+      <c r="N60">
+        <v>15.631743261551108</v>
       </c>
       <c r="O60" s="1">
         <v>1586769589957.783</v>
       </c>
       <c r="P60" s="1">
         <f t="shared" si="0"/>
-        <v>7933847949788914</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+        <v>7933847949788913</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3549,42 +3557,42 @@
       <c r="E61">
         <v>247.01789855957028</v>
       </c>
-      <c r="F61" s="1">
-        <v>193869727153327.5</v>
-      </c>
-      <c r="G61" s="1">
-        <v>6112897622587443</v>
-      </c>
-      <c r="H61" s="1">
+      <c r="F61">
+        <v>6187351136886287</v>
+      </c>
+      <c r="G61">
+        <v>63149768828382.68</v>
+      </c>
+      <c r="H61">
         <v>63149768.828382678</v>
       </c>
-      <c r="I61" s="1">
-        <v>631497688283.82678</v>
-      </c>
-      <c r="J61" s="1">
+      <c r="I61">
+        <v>63149768828.382683</v>
+      </c>
+      <c r="J61">
         <v>27.986228337896019</v>
       </c>
-      <c r="K61" s="1">
-        <v>6314976882838.2686</v>
-      </c>
-      <c r="L61" s="1">
+      <c r="K61">
+        <v>63149768828382.68</v>
+      </c>
+      <c r="L61">
         <v>9.7951799182636066</v>
       </c>
-      <c r="M61" s="1">
+      <c r="M61">
         <v>0.97951799182636057</v>
       </c>
-      <c r="N61" s="1">
-        <v>0</v>
+      <c r="N61">
+        <v>12.442146353180927</v>
       </c>
       <c r="O61" s="1">
         <v>1262995376567.6536</v>
       </c>
       <c r="P61" s="1">
         <f t="shared" si="0"/>
-        <v>6314976882838268</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+        <v>6314976882838269</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>61</v>
       </c>
@@ -3601,22 +3609,22 @@
         <v>244.27033996582031</v>
       </c>
       <c r="F62">
-        <v>153525424931549.41</v>
+        <v>4899762982282964</v>
       </c>
       <c r="G62">
-        <v>4840803248918626</v>
+        <v>50008298026018.867</v>
       </c>
       <c r="H62">
         <v>50008298.026018873</v>
       </c>
       <c r="I62">
-        <v>500082980260.18872</v>
+        <v>50008298026.018875</v>
       </c>
       <c r="J62">
         <v>22.162292488340725</v>
       </c>
       <c r="K62">
-        <v>5000829802601.8867</v>
+        <v>50008298026018.867</v>
       </c>
       <c r="L62">
         <v>7.756802370919254</v>
@@ -3625,17 +3633,17 @@
         <v>0.77568023709192535</v>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>9.8529349268743953</v>
       </c>
       <c r="O62">
         <v>1000165960520.3774</v>
       </c>
       <c r="P62" s="1">
         <f t="shared" si="0"/>
-        <v>5000829802601886</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+        <v>5000829802601887</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>62</v>
       </c>
@@ -3652,22 +3660,22 @@
         <v>241.52363586425781</v>
       </c>
       <c r="F63">
-        <v>120936849272354.16</v>
+        <v>3859698792710158.5</v>
       </c>
       <c r="G63">
-        <v>3813254339680960</v>
+        <v>39393123343811.57</v>
       </c>
       <c r="H63">
         <v>39393123.343811572</v>
       </c>
       <c r="I63">
-        <v>393931233438.11572</v>
+        <v>39393123343.811577</v>
       </c>
       <c r="J63">
         <v>17.457941102506606</v>
       </c>
       <c r="K63">
-        <v>3939312334381.1572</v>
+        <v>39393123343811.57</v>
       </c>
       <c r="L63">
         <v>6.1102793858773126</v>
@@ -3676,17 +3684,17 @@
         <v>0.61102793858773119</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>7.761469519937819</v>
       </c>
       <c r="O63">
         <v>787862466876.23145</v>
       </c>
       <c r="P63" s="1">
         <f t="shared" si="0"/>
-        <v>3939312334381156.5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+        <v>3939312334381157</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>63</v>
       </c>
@@ -3703,22 +3711,22 @@
         <v>238.77778625488281</v>
       </c>
       <c r="F64">
-        <v>94747343493717.172</v>
+        <v>3023860878594858.5</v>
       </c>
       <c r="G64">
-        <v>2987474214224057.5</v>
+        <v>30862336923802.25</v>
       </c>
       <c r="H64">
         <v>30862336.923802249</v>
       </c>
       <c r="I64">
-        <v>308623369238.02252</v>
+        <v>30862336923.802254</v>
       </c>
       <c r="J64">
         <v>13.677332858301925</v>
       </c>
       <c r="K64">
-        <v>3086233692380.2251</v>
+        <v>30862336923802.25</v>
       </c>
       <c r="L64">
         <v>4.7870665004056736</v>
@@ -3727,17 +3735,17 @@
         <v>0.47870665004056739</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>6.0806827947490625</v>
       </c>
       <c r="O64">
         <v>617246738476.04504</v>
       </c>
       <c r="P64" s="1">
         <f t="shared" si="0"/>
-        <v>3086233692380224.5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+        <v>3086233692380225.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>64</v>
       </c>
@@ -3754,22 +3762,22 @@
         <v>236.03280639648438</v>
       </c>
       <c r="F65">
-        <v>73811526141143.406</v>
+        <v>2355694397937243.5</v>
       </c>
       <c r="G65">
-        <v>2327347901567427</v>
+        <v>24042850222804</v>
       </c>
       <c r="H65">
         <v>24042850.222803999</v>
       </c>
       <c r="I65">
-        <v>240428502228.04001</v>
+        <v>24042850222.804001</v>
       </c>
       <c r="J65">
         <v>10.655125247692212</v>
       </c>
       <c r="K65">
-        <v>2404285022280.3999</v>
+        <v>24042850222804</v>
       </c>
       <c r="L65">
         <v>3.7292938366922739</v>
@@ -3778,7 +3786,7 @@
         <v>0.3729293836692274</v>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>4.7370666079981811</v>
       </c>
       <c r="O65">
         <v>480857004456.08002</v>
@@ -3788,7 +3796,7 @@
         <v>2404285022280399.5</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>65</v>
       </c>
@@ -3805,22 +3813,22 @@
         <v>233.2886657714844</v>
       </c>
       <c r="F66">
-        <v>57166844765321.945</v>
+        <v>1824479495301366.5</v>
       </c>
       <c r="G66">
-        <v>1802525203846732</v>
+        <v>18621128138912.52</v>
       </c>
       <c r="H66">
         <v>18621128.138912521</v>
       </c>
       <c r="I66">
-        <v>186211281389.12521</v>
+        <v>18621128138.912521</v>
       </c>
       <c r="J66">
         <v>8.2523681982284973</v>
       </c>
       <c r="K66">
-        <v>1862112813891.252</v>
+        <v>18621128138912.52</v>
       </c>
       <c r="L66">
         <v>2.8883288693799738</v>
@@ -3829,17 +3837,17 @@
         <v>0.28883288693799741</v>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>3.6688463926973784</v>
       </c>
       <c r="O66">
         <v>372422562778.25043</v>
       </c>
       <c r="P66" s="1">
         <f t="shared" si="0"/>
-        <v>1862112813891252.5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1862112813891252.3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>66</v>
       </c>
@@ -3856,22 +3864,22 @@
         <v>230.54537963867188</v>
       </c>
       <c r="F67">
-        <v>44008650597821.172</v>
+        <v>1404535810244919</v>
       </c>
       <c r="G67">
-        <v>1387634777037365.8</v>
+        <v>14335070010716.588</v>
       </c>
       <c r="H67">
         <v>14335070.010716587</v>
       </c>
       <c r="I67">
-        <v>143350700107.16589</v>
+        <v>14335070010.716589</v>
       </c>
       <c r="J67">
         <v>6.3529059567883559</v>
       </c>
       <c r="K67">
-        <v>1433507001071.6587</v>
+        <v>14335070010716.588</v>
       </c>
       <c r="L67">
         <v>2.2235170848759243</v>
@@ -3880,17 +3888,17 @@
         <v>0.22235170848759245</v>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.8243815039314466</v>
       </c>
       <c r="O67">
         <v>286701400214.33179</v>
       </c>
       <c r="P67" s="1">
         <f t="shared" ref="P67:P101" si="1">SUM(F67:O67)</f>
-        <v>1433507001071659</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1433507001071658.5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>67</v>
       </c>
@@ -3907,22 +3915,22 @@
         <v>227.80293273925781</v>
       </c>
       <c r="F68">
-        <v>33667570847583.828</v>
+        <v>1074500314302536.5</v>
       </c>
       <c r="G68">
-        <v>1061570657855837</v>
+        <v>10966639027436.332</v>
       </c>
       <c r="H68">
         <v>10966639.027436333</v>
       </c>
       <c r="I68">
-        <v>109666390274.36333</v>
+        <v>10966639027.436333</v>
       </c>
       <c r="J68">
         <v>4.8601106483096439</v>
       </c>
       <c r="K68">
-        <v>1096663902743.6333</v>
+        <v>10966639027436.332</v>
       </c>
       <c r="L68">
         <v>1.7010387269083755</v>
@@ -3931,17 +3939,17 @@
         <v>0.17010387269083754</v>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2.1607130210196712</v>
       </c>
       <c r="O68">
         <v>219332780548.72665</v>
       </c>
       <c r="P68" s="1">
         <f t="shared" si="1"/>
-        <v>1096663902743633.4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1096663902743633.3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>68</v>
       </c>
@@ -3958,22 +3966,22 @@
         <v>225.06135559082031</v>
       </c>
       <c r="F69">
-        <v>25589858666528.109</v>
+        <v>816700180260116.13</v>
       </c>
       <c r="G69">
-        <v>806872679411430.63</v>
+        <v>8335461564167.6729</v>
       </c>
       <c r="H69">
         <v>8335461.5641676728</v>
       </c>
       <c r="I69">
-        <v>83354615641.676727</v>
+        <v>8335461564.1676731</v>
       </c>
       <c r="J69">
         <v>3.6940456784650251</v>
       </c>
       <c r="K69">
-        <v>833546156416.76721</v>
+        <v>8335461564167.6729</v>
       </c>
       <c r="L69">
         <v>1.2929159874627587</v>
@@ -3982,7 +3990,7 @@
         <v>0.12929159874627588</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1.6423026501417</v>
       </c>
       <c r="O69">
         <v>166709231283.35345</v>
@@ -3992,7 +4000,7 @@
         <v>833546156416767.25</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>69</v>
       </c>
@@ -4009,22 +4017,22 @@
         <v>222.32064819335938</v>
       </c>
       <c r="F70">
-        <v>19319840052903.922</v>
+        <v>616592575184550</v>
       </c>
       <c r="G70">
-        <v>609173005307647</v>
+        <v>6293109558963.2949</v>
       </c>
       <c r="H70">
         <v>6293109.5589632951</v>
       </c>
       <c r="I70">
-        <v>62931095589.63295</v>
+        <v>6293109558.9632959</v>
       </c>
       <c r="J70">
         <v>2.7889318415586271</v>
       </c>
       <c r="K70">
-        <v>629310955896.32947</v>
+        <v>6293109558963.2949</v>
       </c>
       <c r="L70">
         <v>0.97612614454551938</v>
@@ -4033,17 +4041,17 @@
         <v>9.7612614454551938E-2</v>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1.2399062039643023</v>
       </c>
       <c r="O70">
         <v>125862191179.2659</v>
       </c>
       <c r="P70" s="1">
         <f t="shared" si="1"/>
-        <v>629310955896329.5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+        <v>629310955896329.38</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>70</v>
       </c>
@@ -4060,22 +4068,22 @@
         <v>219.58074951171875</v>
       </c>
       <c r="F71">
-        <v>14484699175758.314</v>
+        <v>462279084148625.06</v>
       </c>
       <c r="G71">
-        <v>456716396394162.75</v>
+        <v>4718144590848.7891</v>
       </c>
       <c r="H71">
         <v>4718144.5908487886</v>
       </c>
       <c r="I71">
-        <v>47181445908.487892</v>
+        <v>4718144590.8487892</v>
       </c>
       <c r="J71">
         <v>2.0909509931785593</v>
       </c>
       <c r="K71">
-        <v>471814459084.87891</v>
+        <v>4718144590848.7891</v>
       </c>
       <c r="L71">
         <v>0.73183284761249567</v>
@@ -4084,17 +4092,17 @@
         <v>7.3183284761249578E-2</v>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>0.92959715615657357</v>
       </c>
       <c r="O71">
         <v>94362891816.975784</v>
       </c>
       <c r="P71" s="1">
         <f t="shared" si="1"/>
-        <v>471814459084878.88</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+        <v>471814459084878.94</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>71</v>
       </c>
@@ -4111,22 +4119,22 @@
         <v>216.84172058105469</v>
       </c>
       <c r="F72">
-        <v>10781363049883.469</v>
+        <v>344087134713519.56</v>
       </c>
       <c r="G72">
-        <v>339946672044169.06</v>
+        <v>3511845785580.2588</v>
       </c>
       <c r="H72">
         <v>3511845.7855802588</v>
       </c>
       <c r="I72">
-        <v>35118457855.802589</v>
+        <v>3511845785.5802588</v>
       </c>
       <c r="J72">
         <v>1.5563527763628722</v>
       </c>
       <c r="K72">
-        <v>351184578558.02588</v>
+        <v>3511845785580.2588</v>
       </c>
       <c r="L72">
         <v>0.54472347172700519</v>
@@ -4135,7 +4143,7 @@
         <v>5.4472347172700525E-2</v>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>0.69192492774973613</v>
       </c>
       <c r="O72">
         <v>70236915711.605179</v>
@@ -4145,7 +4153,7 @@
         <v>351184578558025.94</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>72</v>
       </c>
@@ -4162,22 +4170,22 @@
         <v>214.25968933105469</v>
       </c>
       <c r="F73">
-        <v>8031834492872.0586</v>
+        <v>256335947909242.56</v>
       </c>
       <c r="G73">
-        <v>253251411127550.75</v>
+        <v>2616233586028.417</v>
       </c>
       <c r="H73">
         <v>2616233.5860284171</v>
       </c>
       <c r="I73">
-        <v>26162335860.284168</v>
+        <v>2616233586.0284171</v>
       </c>
       <c r="J73">
         <v>1.1594422573872625</v>
       </c>
       <c r="K73">
-        <v>261623358602.84171</v>
+        <v>2616233586028.417</v>
       </c>
       <c r="L73">
         <v>0.40580479008554188</v>
@@ -4186,17 +4194,17 @@
         <v>4.0580479008554188E-2</v>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>0.51546603852083495</v>
       </c>
       <c r="O73">
         <v>52324671720.568336</v>
       </c>
       <c r="P73" s="1">
         <f t="shared" si="1"/>
-        <v>261623358602841.69</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+        <v>261623358602841.66</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>73</v>
       </c>
@@ -4213,22 +4221,22 @@
         <v>212.304443359375</v>
       </c>
       <c r="F74">
-        <v>6151070175096.4912</v>
+        <v>196311366399410.41</v>
       </c>
       <c r="G74">
-        <v>193949116253607.41</v>
+        <v>2003606572867.8455</v>
       </c>
       <c r="H74">
         <v>2003606.5728678454</v>
       </c>
       <c r="I74">
-        <v>20036065728.678455</v>
+        <v>2003606572.8678455</v>
       </c>
       <c r="J74">
         <v>0.88794293451770512</v>
       </c>
       <c r="K74">
-        <v>200360657286.78455</v>
+        <v>2003606572867.8455</v>
       </c>
       <c r="L74">
         <v>0.31078002708119679</v>
@@ -4237,7 +4245,7 @@
         <v>3.1078002708119678E-2</v>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>0.39476258862586011</v>
       </c>
       <c r="O74">
         <v>40072131457.356911</v>
@@ -4247,7 +4255,7 @@
         <v>200360657286784.5</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>74</v>
       </c>
@@ -4264,22 +4272,22 @@
         <v>210.34982299804688</v>
       </c>
       <c r="F75">
-        <v>4687574429055.0615</v>
+        <v>149603908762478.06</v>
       </c>
       <c r="G75">
-        <v>147803697894566.09</v>
+        <v>1526897705522.3772</v>
       </c>
       <c r="H75">
         <v>1526897.7055223773</v>
       </c>
       <c r="I75">
-        <v>15268977055.223772</v>
+        <v>1526897705.5223773</v>
       </c>
       <c r="J75">
         <v>0.67667876903062874</v>
       </c>
       <c r="K75">
-        <v>152689770552.23773</v>
+        <v>1526897705522.3772</v>
       </c>
       <c r="L75">
         <v>0.23683756916072005</v>
@@ -4288,17 +4296,17 @@
         <v>2.3683756916072007E-2</v>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>0.30083854732825194</v>
       </c>
       <c r="O75">
         <v>30537954110.447544</v>
       </c>
       <c r="P75" s="1">
         <f t="shared" si="1"/>
-        <v>152689770552237.75</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+        <v>152689770552237.78</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>75</v>
       </c>
@@ -4315,22 +4323,22 @@
         <v>208.39579772949219</v>
       </c>
       <c r="F76">
-        <v>3554244857798.0615</v>
+        <v>113433702541276.95</v>
       </c>
       <c r="G76">
-        <v>112068734300864.81</v>
+        <v>1157734858480.0085</v>
       </c>
       <c r="H76">
         <v>1157734.8584800086</v>
       </c>
       <c r="I76">
-        <v>11577348584.800085</v>
+        <v>1157734858.4800086</v>
       </c>
       <c r="J76">
         <v>0.51307602078823089</v>
       </c>
       <c r="K76">
-        <v>115773485848.00084</v>
+        <v>1157734858480.0085</v>
       </c>
       <c r="L76">
         <v>0.17957660727588082</v>
@@ -4339,17 +4347,17 @@
         <v>1.795766072758808E-2</v>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>0.22810386822688217</v>
       </c>
       <c r="O76">
         <v>23154697169.60017</v>
       </c>
       <c r="P76" s="1">
         <f t="shared" si="1"/>
-        <v>115773485848000.83</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+        <v>115773485848000.86</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>76</v>
       </c>
@@ -4366,22 +4374,22 @@
         <v>206.44239807128909</v>
       </c>
       <c r="F77">
-        <v>2680943168985.0166</v>
+        <v>85562284571783.172</v>
       </c>
       <c r="G77">
-        <v>84532698140227.781</v>
+        <v>873271675002.35315</v>
       </c>
       <c r="H77">
         <v>873271.67500235315</v>
       </c>
       <c r="I77">
-        <v>8732716750.023531</v>
+        <v>873271675.00235319</v>
       </c>
       <c r="J77">
         <v>0.38700981731303508</v>
       </c>
       <c r="K77">
-        <v>87327167500.235321</v>
+        <v>873271675002.35315</v>
       </c>
       <c r="L77">
         <v>0.13545343605956225</v>
@@ -4390,7 +4398,7 @@
         <v>1.3545343605956228E-2</v>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>0.17205722503901363</v>
       </c>
       <c r="O77">
         <v>17465433500.047062</v>
@@ -4400,7 +4408,7 @@
         <v>87327167500235.328</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>77</v>
       </c>
@@ -4417,22 +4425,22 @@
         <v>204.48957824707031</v>
       </c>
       <c r="F78">
-        <v>2011426217033.9666</v>
+        <v>64194655212390.07</v>
       </c>
       <c r="G78">
-        <v>63422189326096.398</v>
+        <v>655187906261.32654</v>
       </c>
       <c r="H78">
         <v>655187.90626132651</v>
       </c>
       <c r="I78">
-        <v>6551879062.613265</v>
+        <v>655187906.26132655</v>
       </c>
       <c r="J78">
         <v>0.29036113178321354</v>
       </c>
       <c r="K78">
-        <v>65518790626.132652</v>
+        <v>655187906261.32654</v>
       </c>
       <c r="L78">
         <v>0.10162639612412475</v>
@@ -4441,17 +4449,17 @@
         <v>1.0162639612412474E-2</v>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>0.12908905241904411</v>
       </c>
       <c r="O78">
         <v>13103758125.22653</v>
       </c>
       <c r="P78" s="1">
         <f t="shared" si="1"/>
-        <v>65518790626132.641</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+        <v>65518790626132.648</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>78</v>
       </c>
@@ -4468,22 +4476,22 @@
         <v>202.53738403320315</v>
       </c>
       <c r="F79">
-        <v>1500831677777.5271</v>
+        <v>47899033666187.07</v>
       </c>
       <c r="G79">
-        <v>47322655938615.438</v>
+        <v>488870412589.0025</v>
       </c>
       <c r="H79">
         <v>488870.41258900252</v>
       </c>
       <c r="I79">
-        <v>4888704125.8900251</v>
+        <v>488870412.58900255</v>
       </c>
       <c r="J79">
         <v>0.21665382547224851</v>
       </c>
       <c r="K79">
-        <v>48887041258.900253</v>
+        <v>488870412589.0025</v>
       </c>
       <c r="L79">
         <v>7.5828838915286967E-2</v>
@@ -4492,7 +4500,7 @@
         <v>7.5828838915286976E-3</v>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>9.6320181910760819E-2</v>
       </c>
       <c r="O79">
         <v>9777408251.7800503</v>
@@ -4502,7 +4510,7 @@
         <v>48887041258900.25</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>79</v>
       </c>
@@ -4519,22 +4527,22 @@
         <v>200.58578491210938</v>
       </c>
       <c r="F80">
-        <v>1113529714437.0549</v>
+        <v>35538293913880.516</v>
       </c>
       <c r="G80">
-        <v>35110655201362.711</v>
+        <v>362713380179.36688</v>
       </c>
       <c r="H80">
         <v>362713.38017936685</v>
       </c>
       <c r="I80">
-        <v>3627133801.7936687</v>
+        <v>362713380.17936689</v>
       </c>
       <c r="J80">
         <v>0.16074452317468324</v>
       </c>
       <c r="K80">
-        <v>36271338017.936691</v>
+        <v>362713380179.36688</v>
       </c>
       <c r="L80">
         <v>5.6260583111139129E-2</v>
@@ -4543,7 +4551,7 @@
         <v>5.626058311113913E-3</v>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>7.1463966443219951E-2</v>
       </c>
       <c r="O80">
         <v>7254267603.5873375</v>
@@ -4553,7 +4561,7 @@
         <v>36271338017936.695</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>80</v>
       </c>
@@ -4570,22 +4578,22 @@
         <v>198.63479614257813</v>
       </c>
       <c r="F81">
-        <v>821377397507.96008</v>
+        <v>26214254535284.977</v>
       </c>
       <c r="G81">
-        <v>25898813673485.34</v>
+        <v>267549728031.87335</v>
       </c>
       <c r="H81">
         <v>267549.72803187335</v>
       </c>
       <c r="I81">
-        <v>2675497280.3187337</v>
+        <v>267549728.03187338</v>
       </c>
       <c r="J81">
         <v>0.1185706285131583</v>
       </c>
       <c r="K81">
-        <v>26754972803.187336</v>
+        <v>267549728031.87335</v>
       </c>
       <c r="L81">
         <v>4.1499719979605401E-2</v>
@@ -4594,7 +4602,7 @@
         <v>4.1499719979605403E-3</v>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>5.2714252715207882E-2</v>
       </c>
       <c r="O81">
         <v>5350994560.6374674</v>
@@ -4604,7 +4612,7 @@
         <v>26754972803187.336</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>81</v>
       </c>
@@ -4621,22 +4629,22 @@
         <v>196.68441772460938</v>
       </c>
       <c r="F82">
-        <v>602255499904.30176</v>
+        <v>19220980535459.234</v>
       </c>
       <c r="G82">
-        <v>18989691003400.324</v>
+        <v>196174493836.78021</v>
       </c>
       <c r="H82">
         <v>196174.4938367802</v>
       </c>
       <c r="I82">
-        <v>1961744938.3678021</v>
+        <v>196174493.83678022</v>
       </c>
       <c r="J82">
         <v>8.6939101764688345E-2</v>
       </c>
       <c r="K82">
-        <v>19617449383.67802</v>
+        <v>196174493836.78021</v>
       </c>
       <c r="L82">
         <v>3.0428685617640918E-2</v>
@@ -4645,7 +4653,7 @@
         <v>3.0428685617640921E-3</v>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>3.8651475822685459E-2</v>
       </c>
       <c r="O82">
         <v>3923489876.7356043</v>
@@ -4655,7 +4663,7 @@
         <v>19617449383678.02</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>82</v>
       </c>
@@ -4672,22 +4680,22 @@
         <v>194.73463439941406</v>
       </c>
       <c r="F83">
-        <v>438872592143.69269</v>
+        <v>14006616049966.941</v>
       </c>
       <c r="G83">
-        <v>13838071908009.705</v>
+        <v>142955288305.88541</v>
       </c>
       <c r="H83">
         <v>142955.28830588539</v>
       </c>
       <c r="I83">
-        <v>1429552883.0588539</v>
+        <v>142955288.3058854</v>
       </c>
       <c r="J83">
         <v>6.3353824010201495E-2</v>
       </c>
       <c r="K83">
-        <v>14295528830.588539</v>
+        <v>142955288305.88541</v>
       </c>
       <c r="L83">
         <v>2.2173838403570525E-2</v>
@@ -4696,7 +4704,7 @@
         <v>2.2173838403570525E-3</v>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.8165908633755378E-2</v>
       </c>
       <c r="O83">
         <v>2859105766.1177077</v>
@@ -4706,7 +4714,7 @@
         <v>14295528830588.537</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>83</v>
       </c>
@@ -4723,22 +4731,22 @@
         <v>192.78546142578125</v>
       </c>
       <c r="F84">
-        <v>317787094700.61584</v>
+        <v>10142173151812.254</v>
       </c>
       <c r="G84">
-        <v>10020130549562.303</v>
+        <v>103513745346.71802</v>
       </c>
       <c r="H84">
         <v>103513.74534671802</v>
       </c>
       <c r="I84">
-        <v>1035137453.4671801</v>
+        <v>103513745.34671801</v>
       </c>
       <c r="J84">
         <v>4.5874424675360528E-2</v>
       </c>
       <c r="K84">
-        <v>10351374534.671801</v>
+        <v>103513745346.71802</v>
       </c>
       <c r="L84">
         <v>1.6056048636376184E-2</v>
@@ -4747,17 +4755,17 @@
         <v>1.6056048636376185E-3</v>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.0394899190682464E-2</v>
       </c>
       <c r="O84">
         <v>2070274906.9343603</v>
       </c>
       <c r="P84" s="1">
         <f t="shared" si="1"/>
-        <v>10351374534671.799</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+        <v>10351374534671.801</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>84</v>
       </c>
@@ -4774,22 +4782,22 @@
         <v>190.83688354492188</v>
       </c>
       <c r="F85">
-        <v>228607471952.45047</v>
+        <v>7296006046199.3428</v>
       </c>
       <c r="G85">
-        <v>7208211887040.2236</v>
+        <v>74464998833.060165</v>
       </c>
       <c r="H85">
         <v>74464.998833060163</v>
       </c>
       <c r="I85">
-        <v>744649988.33060169</v>
+        <v>74464998.833060175</v>
       </c>
       <c r="J85">
         <v>3.3000824851579354E-2</v>
       </c>
       <c r="K85">
-        <v>7446499883.3060169</v>
+        <v>74464998833.060165</v>
       </c>
       <c r="L85">
         <v>1.1550288698052772E-2</v>
@@ -4798,17 +4806,17 @@
         <v>1.1550288698052773E-3</v>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.4671540860082514E-2</v>
       </c>
       <c r="O85">
         <v>1489299976.6612034</v>
       </c>
       <c r="P85" s="1">
         <f t="shared" si="1"/>
-        <v>7446499883306.0166</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+        <v>7446499883306.0176</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>85</v>
       </c>
@@ -4825,22 +4833,22 @@
         <v>191</v>
       </c>
       <c r="F86">
-        <v>193619570450.98337</v>
+        <v>6179367387286.0996</v>
       </c>
       <c r="G86">
-        <v>6105009942888.877</v>
+        <v>63068284533.976006</v>
       </c>
       <c r="H86">
         <v>63068.28453397601</v>
       </c>
       <c r="I86">
-        <v>630682845.33976007</v>
+        <v>63068284.533976011</v>
       </c>
       <c r="J86">
         <v>2.795011675567606E-2</v>
       </c>
       <c r="K86">
-        <v>6306828453.3976011</v>
+        <v>63068284533.976006</v>
       </c>
       <c r="L86">
         <v>9.7825408644866205E-3</v>
@@ -4849,7 +4857,7 @@
         <v>9.7825408644866205E-4</v>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>1.2426091828591158E-2</v>
       </c>
       <c r="O86">
         <v>1261365690.6795201</v>
@@ -4859,7 +4867,7 @@
         <v>6306828453397.6006</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>86</v>
       </c>
@@ -4876,22 +4884,22 @@
         <v>190</v>
       </c>
       <c r="F87">
-        <v>149296156966.17886</v>
+        <v>4764785921459.8652</v>
       </c>
       <c r="G87">
-        <v>4707450391459.0801</v>
+        <v>48630685862.18058</v>
       </c>
       <c r="H87">
         <v>48630.68586218058</v>
       </c>
       <c r="I87">
-        <v>486306858.62180579</v>
+        <v>48630685.862180583</v>
       </c>
       <c r="J87">
         <v>2.1551772936273684E-2</v>
       </c>
       <c r="K87">
-        <v>4863068586.2180576</v>
+        <v>48630685862.18058</v>
       </c>
       <c r="L87">
         <v>7.5431205276957885E-3</v>
@@ -4900,7 +4908,7 @@
         <v>7.5431205276957889E-4</v>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>9.5815095126819908E-3</v>
       </c>
       <c r="O87">
         <v>972613717.24361157</v>
@@ -4910,7 +4918,7 @@
         <v>4863068586218.0576</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>87</v>
       </c>
@@ -4927,22 +4935,22 @@
         <v>188</v>
       </c>
       <c r="F88">
-        <v>105585881409.79129</v>
+        <v>3369772748807.4189</v>
       </c>
       <c r="G88">
-        <v>3329223664395.2739</v>
+        <v>34392806450.364403</v>
       </c>
       <c r="H88">
         <v>34392.806450364398</v>
       </c>
       <c r="I88">
-        <v>343928064.50364399</v>
+        <v>34392806.450364403</v>
       </c>
       <c r="J88">
         <v>1.5241939160802661E-2</v>
       </c>
       <c r="K88">
-        <v>3439280645.0364399</v>
+        <v>34392806450.364403</v>
       </c>
       <c r="L88">
         <v>5.3346787062809311E-3</v>
@@ -4951,17 +4959,17 @@
         <v>5.3346787062809309E-4</v>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>6.776277083689497E-3</v>
       </c>
       <c r="O88">
         <v>687856129.00728798</v>
       </c>
       <c r="P88" s="1">
         <f t="shared" si="1"/>
-        <v>3439280645036.4404</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+        <v>3439280645036.4395</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>88</v>
       </c>
@@ -4978,22 +4986,22 @@
         <v>187</v>
       </c>
       <c r="F89">
-        <v>80813837984.833389</v>
+        <v>2579173136897.9795</v>
       </c>
       <c r="G89">
-        <v>2548137480479.1226</v>
+        <v>26323734302.470276</v>
       </c>
       <c r="H89">
         <v>26323.734302470275</v>
       </c>
       <c r="I89">
-        <v>263237343.02470276</v>
+        <v>26323734.302470274</v>
       </c>
       <c r="J89">
         <v>1.1665949892819372E-2</v>
       </c>
       <c r="K89">
-        <v>2632373430.2470274</v>
+        <v>26323734302.470276</v>
       </c>
       <c r="L89">
         <v>4.0830824624867798E-3</v>
@@ -5002,17 +5010,17 @@
         <v>4.0830824624867799E-4</v>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>5.1864600746785085E-3</v>
       </c>
       <c r="O89">
         <v>526474686.04940552</v>
       </c>
       <c r="P89" s="1">
         <f t="shared" si="1"/>
-        <v>2632373430247.0278</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+        <v>2632373430247.0273</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>89</v>
       </c>
@@ -5029,22 +5037,22 @@
         <v>187</v>
       </c>
       <c r="F90">
-        <v>67313441963.312553</v>
+        <v>2148308081797.8162</v>
       </c>
       <c r="G90">
-        <v>2122457102445.2937</v>
+        <v>21926209736.0051</v>
       </c>
       <c r="H90">
         <v>21926.209736005101</v>
       </c>
       <c r="I90">
-        <v>219262097.36005101</v>
+        <v>21926209.736005101</v>
       </c>
       <c r="J90">
         <v>9.7170888134849431E-3</v>
       </c>
       <c r="K90">
-        <v>2192620973.6005101</v>
+        <v>21926209736.0051</v>
       </c>
       <c r="L90">
         <v>3.4009810847197299E-3</v>
@@ -5053,7 +5061,7 @@
         <v>3.4009810847197299E-4</v>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>4.3200333994461411E-3</v>
       </c>
       <c r="O90">
         <v>438524194.72010201</v>
@@ -5063,7 +5071,7 @@
         <v>2192620973600.5103</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>90</v>
       </c>
@@ -5080,22 +5088,22 @@
         <v>187</v>
       </c>
       <c r="F91">
-        <v>56068361334.337311</v>
+        <v>1789421403430.333</v>
       </c>
       <c r="G91">
-        <v>1767888972330.261</v>
+        <v>18263315829.85807</v>
       </c>
       <c r="H91">
         <v>18263.315829858067</v>
       </c>
       <c r="I91">
-        <v>182633158.29858071</v>
+        <v>18263315.829858072</v>
       </c>
       <c r="J91">
         <v>8.0937956940199465E-3</v>
       </c>
       <c r="K91">
-        <v>1826331582.9858069</v>
+        <v>18263315829.85807</v>
       </c>
       <c r="L91">
         <v>2.8328284929069812E-3</v>
@@ -5104,7 +5112,7 @@
         <v>2.8328284929069814E-4</v>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>3.5983480646936163E-3</v>
       </c>
       <c r="O91">
         <v>365266316.59716141</v>
@@ -5114,7 +5122,7 @@
         <v>1826331582985.8071</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>91</v>
       </c>
@@ -5131,22 +5139,22 @@
         <v>188</v>
       </c>
       <c r="F92">
-        <v>51022194185.724373</v>
+        <v>1628373010252.396</v>
       </c>
       <c r="G92">
-        <v>1608778503569.252</v>
+        <v>16619612640.178223</v>
       </c>
       <c r="H92">
         <v>16619.612640178224</v>
       </c>
       <c r="I92">
-        <v>166196126.40178224</v>
+        <v>16619612.640178224</v>
       </c>
       <c r="J92">
         <v>7.3653519698454097E-3</v>
       </c>
       <c r="K92">
-        <v>1661961264.0178223</v>
+        <v>16619612640.178223</v>
       </c>
       <c r="L92">
         <v>2.5778731894458935E-3</v>
@@ -5155,17 +5163,17 @@
         <v>2.5778731894458932E-4</v>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>3.2744958000437549E-3</v>
       </c>
       <c r="O92">
         <v>332392252.80356449</v>
       </c>
       <c r="P92" s="1">
         <f t="shared" si="1"/>
-        <v>1661961264017.8223</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1661961264017.822</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>92</v>
       </c>
@@ -5182,22 +5190,22 @@
         <v>189</v>
       </c>
       <c r="F93">
-        <v>46476543833.472992</v>
+        <v>1483298607518.821</v>
       </c>
       <c r="G93">
-        <v>1465449807339.051</v>
+        <v>15138944290.692677</v>
       </c>
       <c r="H93">
         <v>15138.944290692676</v>
       </c>
       <c r="I93">
-        <v>151389442.90692675</v>
+        <v>15138944.290692678</v>
       </c>
       <c r="J93">
         <v>6.7091607708877083E-3</v>
       </c>
       <c r="K93">
-        <v>1513894429.0692675</v>
+        <v>15138944290.692677</v>
       </c>
       <c r="L93">
         <v>2.3482062698106979E-3</v>
@@ -5206,17 +5214,17 @@
         <v>2.3482062698106977E-4</v>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.9827656378180155E-3</v>
       </c>
       <c r="O93">
         <v>302778885.8138535</v>
       </c>
       <c r="P93" s="1">
         <f t="shared" si="1"/>
-        <v>1513894429069.2678</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1513894429069.2676</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>93</v>
       </c>
@@ -5233,22 +5241,22 @@
         <v>189</v>
       </c>
       <c r="F94">
-        <v>38787334178.320595</v>
+        <v>1237897529175.437</v>
       </c>
       <c r="G94">
-        <v>1223001684515.9165</v>
+        <v>12634314922.685087</v>
       </c>
       <c r="H94">
         <v>12634.314922685087</v>
       </c>
       <c r="I94">
-        <v>126343149.22685088</v>
+        <v>12634314.922685089</v>
       </c>
       <c r="J94">
         <v>5.5991784115642278E-3</v>
       </c>
       <c r="K94">
-        <v>1263431492.2685089</v>
+        <v>12634314922.685087</v>
       </c>
       <c r="L94">
         <v>1.9597124440474799E-3</v>
@@ -5257,17 +5265,17 @@
         <v>1.9597124440474798E-4</v>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>2.4892885319569525E-3</v>
       </c>
       <c r="O94">
         <v>252686298.45370176</v>
       </c>
       <c r="P94" s="1">
         <f t="shared" si="1"/>
-        <v>1263431492268.5088</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1263431492268.5085</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>94</v>
       </c>
@@ -5284,22 +5292,22 @@
         <v>190</v>
       </c>
       <c r="F95">
-        <v>35400108779.084488</v>
+        <v>1129794251615.8704</v>
       </c>
       <c r="G95">
-        <v>1116199233229.7368</v>
+        <v>11530983814.356785</v>
       </c>
       <c r="H95">
         <v>11530.983814356785</v>
       </c>
       <c r="I95">
-        <v>115309838.14356785</v>
+        <v>11530983.814356785</v>
       </c>
       <c r="J95">
         <v>5.1102126258953245E-3</v>
       </c>
       <c r="K95">
-        <v>1153098381.4356785</v>
+        <v>11530983814.356785</v>
       </c>
       <c r="L95">
         <v>1.7885744190633635E-3</v>
@@ -5308,17 +5316,17 @@
         <v>1.7885744190633635E-4</v>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>2.2719036170074599E-3</v>
       </c>
       <c r="O95">
         <v>230619676.28713569</v>
       </c>
       <c r="P95" s="1">
         <f t="shared" si="1"/>
-        <v>1153098381435.6787</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1153098381435.6785</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>95</v>
       </c>
@@ -5335,22 +5343,22 @@
         <v>191</v>
       </c>
       <c r="F96">
-        <v>32339612695.807125</v>
+        <v>1032118538143.9788</v>
       </c>
       <c r="G96">
-        <v>1019698869268.2804</v>
+        <v>10534079227.978104</v>
       </c>
       <c r="H96">
         <v>10534.079227978104</v>
       </c>
       <c r="I96">
-        <v>105340792.27978103</v>
+        <v>10534079.227978105</v>
       </c>
       <c r="J96">
         <v>4.6684121268102024E-3</v>
       </c>
       <c r="K96">
-        <v>1053407922.7978103</v>
+        <v>10534079227.978104</v>
       </c>
       <c r="L96">
         <v>1.6339442443835707E-3</v>
@@ -5359,7 +5367,7 @@
         <v>1.6339442443835707E-4</v>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>2.075487493971614E-3</v>
       </c>
       <c r="O96">
         <v>210681584.55956206</v>
@@ -5369,7 +5377,7 @@
         <v>1053407922797.8103</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>96</v>
       </c>
@@ -5386,22 +5394,22 @@
         <v>192</v>
       </c>
       <c r="F97">
-        <v>29571550255.768719</v>
+        <v>943775842578.11304</v>
       </c>
       <c r="G97">
-        <v>932419217321.88855</v>
+        <v>9632429931.0112457</v>
       </c>
       <c r="H97">
         <v>9632.4299310112456</v>
       </c>
       <c r="I97">
-        <v>96324299.310112461</v>
+        <v>9632429.9310112465</v>
       </c>
       <c r="J97">
         <v>4.2688261334838645E-3</v>
       </c>
       <c r="K97">
-        <v>963242993.10112453</v>
+        <v>9632429931.0112457</v>
       </c>
       <c r="L97">
         <v>1.4940891467193525E-3</v>
@@ -5410,17 +5418,17 @@
         <v>1.4940891467193524E-4</v>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.8978391395874218E-3</v>
       </c>
       <c r="O97">
         <v>192648598.62022492</v>
       </c>
       <c r="P97" s="1">
         <f t="shared" si="1"/>
-        <v>963242993101.12439</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+        <v>963242993101.12451</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>97</v>
       </c>
@@ -5437,22 +5445,22 @@
         <v>193</v>
       </c>
       <c r="F98">
-        <v>27065501114.877628</v>
+        <v>863795299825.69983</v>
       </c>
       <c r="G98">
-        <v>853401094893.08459</v>
+        <v>8816127013.3583126</v>
       </c>
       <c r="H98">
         <v>8816.1270133583112</v>
       </c>
       <c r="I98">
-        <v>88161270.133583128</v>
+        <v>8816127.0133583117</v>
       </c>
       <c r="J98">
         <v>3.9070632914311801E-3</v>
       </c>
       <c r="K98">
-        <v>881612701.33583117</v>
+        <v>8816127013.3583126</v>
       </c>
       <c r="L98">
         <v>1.3674721520009129E-3</v>
@@ -5461,17 +5469,17 @@
         <v>1.3674721520009131E-4</v>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.7370062409339348E-3</v>
       </c>
       <c r="O98">
         <v>176322540.26716626</v>
       </c>
       <c r="P98" s="1">
         <f t="shared" si="1"/>
-        <v>881612701335.83118</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+        <v>881612701335.83093</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>98</v>
       </c>
@@ -5488,22 +5496,22 @@
         <v>193</v>
       </c>
       <c r="F99">
-        <v>22672532452.097019</v>
+        <v>723593732262.42224</v>
       </c>
       <c r="G99">
-        <v>714886598127.04407</v>
+        <v>7385192129.4116125</v>
       </c>
       <c r="H99">
         <v>7385.1921294116128</v>
       </c>
       <c r="I99">
-        <v>73851921.294116125</v>
+        <v>7385192.1294116136</v>
       </c>
       <c r="J99">
         <v>3.2729125868161831E-3</v>
       </c>
       <c r="K99">
-        <v>738519212.94116127</v>
+        <v>7385192129.4116125</v>
       </c>
       <c r="L99">
         <v>1.1455194053856638E-3</v>
@@ -5512,7 +5520,7 @@
         <v>1.145519405385664E-4</v>
       </c>
       <c r="N99">
-        <v>0</v>
+        <v>1.4550748644894525E-3</v>
       </c>
       <c r="O99">
         <v>147703842.58823225</v>
@@ -5522,7 +5530,7 @@
         <v>738519212941.16125</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>99</v>
       </c>
@@ -5539,22 +5547,22 @@
         <v>194</v>
       </c>
       <c r="F100">
-        <v>20789065182.809353</v>
+        <v>663482886071.88477</v>
       </c>
       <c r="G100">
-        <v>655499076610.88647</v>
+        <v>6771684675.7322989</v>
       </c>
       <c r="H100">
         <v>6771.6846757322983</v>
       </c>
       <c r="I100">
-        <v>67716846.757322982</v>
+        <v>6771684.6757322988</v>
       </c>
       <c r="J100">
         <v>3.0010230770963391E-3</v>
       </c>
       <c r="K100">
-        <v>677168467.57322991</v>
+        <v>6771684675.7322989</v>
       </c>
       <c r="L100">
         <v>1.0503580769837186E-3</v>
@@ -5563,17 +5571,17 @@
         <v>1.0503580769837186E-4</v>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.334197944920832E-3</v>
       </c>
       <c r="O100">
         <v>135433693.51464596</v>
       </c>
       <c r="P100" s="1">
         <f t="shared" si="1"/>
-        <v>677168467573.22998</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+        <v>677168467573.2301</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>100</v>
       </c>
@@ -5590,22 +5598,22 @@
         <v>195</v>
       </c>
       <c r="F101">
-        <v>19079025924.655972</v>
+        <v>608906993778.56396</v>
       </c>
       <c r="G101">
-        <v>601579905891.52148</v>
+        <v>6214668449.2925768</v>
       </c>
       <c r="H101">
         <v>6214.668449292577</v>
       </c>
       <c r="I101">
-        <v>62146684.492925771</v>
+        <v>6214668.4492925778</v>
       </c>
       <c r="J101">
         <v>2.7541689145194389E-3</v>
       </c>
       <c r="K101">
-        <v>621466844.92925775</v>
+        <v>6214668449.2925768</v>
       </c>
       <c r="L101">
         <v>9.6395912008180357E-4</v>
@@ -5614,14 +5622,14 @@
         <v>9.6395912008180362E-5</v>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1.2244512658903194E-3</v>
       </c>
       <c r="O101">
         <v>124293368.98585154</v>
       </c>
       <c r="P101" s="1">
         <f t="shared" si="1"/>
-        <v>621466844929.25781</v>
+        <v>621466844929.25793</v>
       </c>
     </row>
   </sheetData>
